--- a/batch_notes/28/batch_28.xlsx
+++ b/batch_notes/28/batch_28.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10728"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10804"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/shira_2/__work__/acciojob/modules/sql/postgresql/batch_notes/28/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF0D360A-A820-BE46-8D8F-4D825F974A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{838724BE-F9F5-1A41-8C1E-35F86F41396D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-2480" windowWidth="38400" windowHeight="21600" xr2:uid="{C88571CB-2605-694D-B9DF-E4D6E422F2C7}"/>
+    <workbookView xWindow="-38400" yWindow="-2480" windowWidth="38400" windowHeight="21600" activeTab="1" xr2:uid="{C88571CB-2605-694D-B9DF-E4D6E422F2C7}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
+    <sheet name="02" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="79">
   <si>
     <t>Warehouse</t>
   </si>
@@ -162,6 +163,120 @@
   </si>
   <si>
     <t>loyalty</t>
+  </si>
+  <si>
+    <t>Steps</t>
+  </si>
+  <si>
+    <t>open git repo</t>
+  </si>
+  <si>
+    <t>https://github.com/starlordali4444/postgresql.git</t>
+  </si>
+  <si>
+    <t>open vs code</t>
+  </si>
+  <si>
+    <t>in vs code click on open folder</t>
+  </si>
+  <si>
+    <t>create sql folder in any location except ondrive</t>
+  </si>
+  <si>
+    <t>open terminal in vs code</t>
+  </si>
+  <si>
+    <t>enter command =&gt; git clone https://github.com/starlordali4444/postgresql.git</t>
+  </si>
+  <si>
+    <t>wait for cloning</t>
+  </si>
+  <si>
+    <t>once done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enter in terminal =&gt; cd postgre </t>
+  </si>
+  <si>
+    <t>press tab</t>
+  </si>
+  <si>
+    <t>psql -U postgres -d postgres -f datasets\v3\sql\setup_accio_retailmart.sql</t>
+  </si>
+  <si>
+    <t>once its completed keep pressing enter to get all the tables</t>
+  </si>
+  <si>
+    <t>then go to pgadmin 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">right click on databases </t>
+  </si>
+  <si>
+    <t>click refresh</t>
+  </si>
+  <si>
+    <t>you will see accio_retailmart_ database</t>
+  </si>
+  <si>
+    <t>click on the above database to connect</t>
+  </si>
+  <si>
+    <t>right click on the above database then click on properties</t>
+  </si>
+  <si>
+    <t>add 28 in the of database name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">click ok </t>
+  </si>
+  <si>
+    <t xml:space="preserve">we are done </t>
+  </si>
+  <si>
+    <t>Books</t>
+  </si>
+  <si>
+    <t>Students</t>
+  </si>
+  <si>
+    <t>Borrowing/Returning</t>
+  </si>
+  <si>
+    <t>Schemas</t>
+  </si>
+  <si>
+    <t>Column2</t>
+  </si>
+  <si>
+    <t>Column3</t>
+  </si>
+  <si>
+    <t>Column4</t>
+  </si>
+  <si>
+    <t>Column5</t>
+  </si>
+  <si>
+    <t>Student_id</t>
+  </si>
+  <si>
+    <t>Ali</t>
+  </si>
+  <si>
+    <t>accio_28</t>
+  </si>
+  <si>
+    <t>shop</t>
+  </si>
+  <si>
+    <t>people</t>
+  </si>
+  <si>
+    <t>transaction</t>
+  </si>
+  <si>
+    <t>table</t>
   </si>
 </sst>
 </file>
@@ -191,7 +306,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -199,13 +314,102 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -238,8 +442,8 @@
       <xdr:row>12</xdr:row>
       <xdr:rowOff>139920</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="2" name="Ink 1">
@@ -258,7 +462,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="2" name="Ink 1">
@@ -303,8 +507,8 @@
       <xdr:row>17</xdr:row>
       <xdr:rowOff>34720</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="3" name="Ink 2">
@@ -323,7 +527,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="3" name="Ink 2">
@@ -368,8 +572,8 @@
       <xdr:row>12</xdr:row>
       <xdr:rowOff>167640</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="4" name="Ink 3">
@@ -388,7 +592,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="4" name="Ink 3">
@@ -418,6 +622,55 @@
         </xdr:pic>
       </mc:Fallback>
     </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>163133</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{050000E6-E3C0-4421-00E1-256041CF8A4B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1651000" y="3048000"/>
+          <a:ext cx="7772400" cy="3617533"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -502,6 +755,20 @@
   </inkml:definitions>
   <inkml:trace contextRef="#ctx0" brushRef="#br0">4094 200 24575,'-5'-5'0,"-4"1"0,-19-9 0,-30-6 0,-33-4 0,32 11 0,-4 3 0,-9 1 0,2 2 0,-23 2 0,37 2 0,4 1 0,1 1 0,-37-8 0,-21-3 0,21 6 0,-6 1 0,-8-1-646,14 1 1,-8-1 0,-3 1 0,0-1 0,3 2 645,9 0 0,3 1 0,0 0 0,-2 0 0,-3 1 0,-1 0 0,-4 1 0,-2 0 0,0 1 0,2-1 0,5 0 0,2 0 0,3 0 0,3 0 0,-1 0 0,0 0-360,-5 0 1,-2-1 0,0 0 0,4 0 0,4 0 359,-20 0 0,7 0 0,9 0 0,0-1 0,16-1 0,16-2 0,16 2 0,15 1 2889,-6-3-2889,15 4 2133,9-1-2133,17 6 0,16-3 0,1 3 0,-6-4 0,-13 0 0</inkml:trace>
 </inkml:ink>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3CF7AC3A-5F42-EF48-A52B-FC82AB433DE0}" name="Table1" displayName="Table1" ref="I67:M79" totalsRowShown="0">
+  <autoFilter ref="I67:M79" xr:uid="{3CF7AC3A-5F42-EF48-A52B-FC82AB433DE0}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{6D6DB51D-16FE-5A42-966B-22D3B6FB2EEC}" name="Student_id"/>
+    <tableColumn id="2" xr3:uid="{F1607987-4049-D149-AB53-6369820C76A7}" name="Column2"/>
+    <tableColumn id="3" xr3:uid="{86AE4211-B9CF-1240-80C4-1BAD3EAB3AEF}" name="Column3"/>
+    <tableColumn id="4" xr3:uid="{61DFAD3D-3AB7-114F-A2F9-1CC2946365B4}" name="Column4"/>
+    <tableColumn id="5" xr3:uid="{1192BE98-3F1F-5849-AEA8-B2AF03CE16F9}" name="Column5"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1061,4 +1328,463 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C30BBE9F-6251-054D-8156-7574F8262F96}">
+  <dimension ref="B2:M88"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B11">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B12">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B13">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B14">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B15">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B34">
+        <v>13</v>
+      </c>
+      <c r="C34" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B35">
+        <v>14</v>
+      </c>
+      <c r="C35" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B36">
+        <v>15</v>
+      </c>
+      <c r="C36" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B37">
+        <v>16</v>
+      </c>
+      <c r="C37" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B38">
+        <v>17</v>
+      </c>
+      <c r="C38" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B39">
+        <v>18</v>
+      </c>
+      <c r="C39" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B40">
+        <v>19</v>
+      </c>
+      <c r="C40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B41">
+        <v>20</v>
+      </c>
+      <c r="C41" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B42">
+        <v>21</v>
+      </c>
+      <c r="C42" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="51" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="D51" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>67</v>
+      </c>
+      <c r="D52" t="s">
+        <v>67</v>
+      </c>
+      <c r="F52" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="53" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B53" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C53" s="4"/>
+      <c r="D53" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E53" s="4"/>
+      <c r="F53" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G53" s="4"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="3"/>
+      <c r="K53" s="3"/>
+      <c r="L53" s="4"/>
+    </row>
+    <row r="54" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B54" s="5"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="7"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6"/>
+      <c r="L54" s="7"/>
+    </row>
+    <row r="55" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B55" s="5"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="7"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="6"/>
+      <c r="K55" s="6"/>
+      <c r="L55" s="7"/>
+    </row>
+    <row r="56" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B56" s="5"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="7"/>
+      <c r="I56" s="5"/>
+      <c r="J56" s="6"/>
+      <c r="K56" s="6"/>
+      <c r="L56" s="7"/>
+    </row>
+    <row r="57" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B57" s="5"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="6"/>
+      <c r="G57" s="7"/>
+      <c r="I57" s="5"/>
+      <c r="J57" s="6"/>
+      <c r="K57" s="6"/>
+      <c r="L57" s="7"/>
+    </row>
+    <row r="58" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B58" s="5"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="7"/>
+      <c r="I58" s="5"/>
+      <c r="J58" s="6"/>
+      <c r="K58" s="6"/>
+      <c r="L58" s="7"/>
+    </row>
+    <row r="59" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B59" s="5"/>
+      <c r="C59" s="7"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="6"/>
+      <c r="G59" s="7"/>
+      <c r="I59" s="5"/>
+      <c r="J59" s="6"/>
+      <c r="K59" s="6"/>
+      <c r="L59" s="7"/>
+    </row>
+    <row r="60" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B60" s="5"/>
+      <c r="C60" s="7"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="7"/>
+      <c r="I60" s="5"/>
+      <c r="J60" s="6"/>
+      <c r="K60" s="6"/>
+      <c r="L60" s="7"/>
+    </row>
+    <row r="61" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B61" s="5"/>
+      <c r="C61" s="7"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="6"/>
+      <c r="G61" s="7"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="6"/>
+      <c r="K61" s="6"/>
+      <c r="L61" s="7"/>
+    </row>
+    <row r="62" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B62" s="5"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="7"/>
+      <c r="I62" s="5"/>
+      <c r="J62" s="6"/>
+      <c r="K62" s="6"/>
+      <c r="L62" s="7"/>
+    </row>
+    <row r="63" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="5"/>
+      <c r="C63" s="7"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="7"/>
+      <c r="I63" s="8"/>
+      <c r="J63" s="9"/>
+      <c r="K63" s="9"/>
+      <c r="L63" s="10"/>
+    </row>
+    <row r="64" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B64" s="5"/>
+      <c r="C64" s="7"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="7"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B65" s="5"/>
+      <c r="C65" s="7"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="7"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="7"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B66" s="5"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="7"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="7"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B67" s="5"/>
+      <c r="C67" s="7"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="7"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="7"/>
+      <c r="I67" t="s">
+        <v>72</v>
+      </c>
+      <c r="J67" t="s">
+        <v>68</v>
+      </c>
+      <c r="K67" t="s">
+        <v>69</v>
+      </c>
+      <c r="L67" t="s">
+        <v>70</v>
+      </c>
+      <c r="M67" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B68" s="5"/>
+      <c r="C68" s="7"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="7"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="7"/>
+      <c r="I68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B69" s="5"/>
+      <c r="C69" s="7"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="7"/>
+      <c r="I69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="8"/>
+      <c r="C70" s="10"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="10"/>
+      <c r="F70" s="9"/>
+      <c r="G70" s="10"/>
+      <c r="I70">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="I71" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="83" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C83" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="84" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="D84" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="85" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="E85" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="86" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="E86" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="87" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="D87" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="88" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="D88" t="s">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/batch_notes/28/batch_28.xlsx
+++ b/batch_notes/28/batch_28.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/shira_2/__work__/acciojob/modules/sql/postgresql/batch_notes/28/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE3C297-8F3A-E049-BE4F-7B6BB6A56901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33391F5C-9BF9-4040-9E83-25B3D02CD98B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-2480" windowWidth="38400" windowHeight="21600" activeTab="8" xr2:uid="{C88571CB-2605-694D-B9DF-E4D6E422F2C7}"/>
+    <workbookView xWindow="-38400" yWindow="-2480" windowWidth="38400" windowHeight="21600" activeTab="9" xr2:uid="{C88571CB-2605-694D-B9DF-E4D6E422F2C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Intro to SQL" sheetId="1" r:id="rId1"/>
@@ -21,13 +21,14 @@
     <sheet name="Scalar Functions" sheetId="6" r:id="rId6"/>
     <sheet name="Conditional Logic &amp; Derived Col" sheetId="7" r:id="rId7"/>
     <sheet name="Aggregate Functions &amp; Group By" sheetId="8" r:id="rId8"/>
-    <sheet name="Join Part 1" sheetId="9" r:id="rId9"/>
+    <sheet name="Join Part 1 &amp; 2" sheetId="9" r:id="rId9"/>
+    <sheet name="Self Join" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId10"/>
-    <pivotCache cacheId="1" r:id="rId11"/>
-    <pivotCache cacheId="2" r:id="rId12"/>
+    <pivotCache cacheId="0" r:id="rId11"/>
+    <pivotCache cacheId="1" r:id="rId12"/>
+    <pivotCache cacheId="2" r:id="rId13"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -74,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="688">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="773">
   <si>
     <t>Warehouse</t>
   </si>
@@ -2168,6 +2169,261 @@
   </si>
   <si>
     <t>c.last_name</t>
+  </si>
+  <si>
+    <t>Tableau</t>
+  </si>
+  <si>
+    <t>Power BI</t>
+  </si>
+  <si>
+    <t>Spot Fire</t>
+  </si>
+  <si>
+    <t>Quicklook</t>
+  </si>
+  <si>
+    <t>AWS</t>
+  </si>
+  <si>
+    <t>GCP</t>
+  </si>
+  <si>
+    <t>Azure</t>
+  </si>
+  <si>
+    <t>Databricks</t>
+  </si>
+  <si>
+    <t>Spark</t>
+  </si>
+  <si>
+    <t>Hadoop</t>
+  </si>
+  <si>
+    <t>Snowflake</t>
+  </si>
+  <si>
+    <t>Fabric</t>
+  </si>
+  <si>
+    <t>MS Office</t>
+  </si>
+  <si>
+    <t>MS Fabric</t>
+  </si>
+  <si>
+    <t>Fact</t>
+  </si>
+  <si>
+    <t>Dimension</t>
+  </si>
+  <si>
+    <t>stores</t>
+  </si>
+  <si>
+    <t>dept</t>
+  </si>
+  <si>
+    <t>customers</t>
+  </si>
+  <si>
+    <t>who placed a order</t>
+  </si>
+  <si>
+    <t>Orders Plced by customer</t>
+  </si>
+  <si>
+    <t>Customner Never placed the order</t>
+  </si>
+  <si>
+    <t>Table2</t>
+  </si>
+  <si>
+    <t>Table3</t>
+  </si>
+  <si>
+    <t>Table4</t>
+  </si>
+  <si>
+    <t>Table5</t>
+  </si>
+  <si>
+    <t>Table6</t>
+  </si>
+  <si>
+    <t>Table7</t>
+  </si>
+  <si>
+    <t>Table8</t>
+  </si>
+  <si>
+    <t>Table9</t>
+  </si>
+  <si>
+    <t>Table10</t>
+  </si>
+  <si>
+    <t>View1</t>
+  </si>
+  <si>
+    <t>View2</t>
+  </si>
+  <si>
+    <t>Normalization</t>
+  </si>
+  <si>
+    <t>Denormalization</t>
+  </si>
+  <si>
+    <t>Cross Join</t>
+  </si>
+  <si>
+    <t>Self-Join</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Union </t>
+  </si>
+  <si>
+    <t>Union All</t>
+  </si>
+  <si>
+    <t>Gamers</t>
+  </si>
+  <si>
+    <t>Games</t>
+  </si>
+  <si>
+    <t>G1</t>
+  </si>
+  <si>
+    <t>G2</t>
+  </si>
+  <si>
+    <t>G3</t>
+  </si>
+  <si>
+    <t>G4</t>
+  </si>
+  <si>
+    <t>G5</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>m x n</t>
+  </si>
+  <si>
+    <t>left</t>
+  </si>
+  <si>
+    <t>right</t>
+  </si>
+  <si>
+    <t>full</t>
+  </si>
+  <si>
+    <t>Same</t>
+  </si>
+  <si>
+    <t>product_id</t>
+  </si>
+  <si>
+    <t>product_name</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>a a</t>
+  </si>
+  <si>
+    <t>a b</t>
+  </si>
+  <si>
+    <t>a c</t>
+  </si>
+  <si>
+    <t>b a</t>
+  </si>
+  <si>
+    <t>b b</t>
+  </si>
+  <si>
+    <t>b c</t>
+  </si>
+  <si>
+    <t>c a</t>
+  </si>
+  <si>
+    <t>c b</t>
+  </si>
+  <si>
+    <t>c c</t>
+  </si>
+  <si>
+    <t>d d</t>
+  </si>
+  <si>
+    <t>d e</t>
+  </si>
+  <si>
+    <t>e d</t>
+  </si>
+  <si>
+    <t>e e</t>
+  </si>
+  <si>
+    <t>p1.category_id =p2.category_id and p1.product_id &lt; p2.product_id</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>brand_id</t>
+  </si>
+  <si>
+    <t>category_id</t>
+  </si>
+  <si>
+    <t>P1 -&gt; P2</t>
+  </si>
+  <si>
+    <t>B1 -&gt; B2</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>category_name</t>
+  </si>
+  <si>
+    <t>Brand</t>
+  </si>
+  <si>
+    <t>Products 1</t>
+  </si>
+  <si>
+    <t>Brand 1</t>
+  </si>
+  <si>
+    <t>Products 2</t>
+  </si>
+  <si>
+    <t>Brand 2</t>
+  </si>
+  <si>
+    <t>Food Taste</t>
   </si>
 </sst>
 </file>
@@ -2237,7 +2493,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2307,6 +2563,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2503,7 +2765,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -2547,14 +2809,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2563,11 +2821,74 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2586,32 +2907,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2625,7 +2922,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2640,45 +2937,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3890,8 +4152,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9156700" y="23348950"/>
-          <a:ext cx="4000500" cy="2286000"/>
+          <a:off x="12052300" y="23583900"/>
+          <a:ext cx="4000500" cy="2297113"/>
           <a:chOff x="7804150" y="23285450"/>
           <a:chExt cx="4000500" cy="2286000"/>
         </a:xfrm>
@@ -4027,8 +4289,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9264650" y="26822400"/>
-          <a:ext cx="4000500" cy="2286000"/>
+          <a:off x="12160250" y="27074813"/>
+          <a:ext cx="4000500" cy="2297112"/>
           <a:chOff x="7804150" y="23285450"/>
           <a:chExt cx="4000500" cy="2286000"/>
         </a:xfrm>
@@ -4142,13 +4404,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>292100</xdr:colOff>
-      <xdr:row>149</xdr:row>
+      <xdr:row>157</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>101600</xdr:colOff>
-      <xdr:row>160</xdr:row>
+      <xdr:row>168</xdr:row>
       <xdr:rowOff>158750</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -4164,8 +4426,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9398000" y="30994350"/>
-          <a:ext cx="4000500" cy="2286000"/>
+          <a:off x="12293600" y="32913638"/>
+          <a:ext cx="4000500" cy="2297112"/>
           <a:chOff x="7804150" y="23285450"/>
           <a:chExt cx="4000500" cy="2286000"/>
         </a:xfrm>
@@ -4279,13 +4541,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>168</xdr:row>
+      <xdr:row>176</xdr:row>
       <xdr:rowOff>93662</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>179</xdr:row>
+      <xdr:row>187</xdr:row>
       <xdr:rowOff>80962</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -4301,8 +4563,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9344025" y="34878962"/>
-          <a:ext cx="4000500" cy="2286000"/>
+          <a:off x="12239625" y="36820475"/>
+          <a:ext cx="4000500" cy="2297112"/>
           <a:chOff x="7804150" y="23285450"/>
           <a:chExt cx="4000500" cy="2286000"/>
         </a:xfrm>
@@ -4425,8 +4687,8 @@
       <xdr:row>118</xdr:row>
       <xdr:rowOff>181962</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="14" name="Ink 13">
@@ -4445,7 +4707,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="14" name="Ink 13">
@@ -4490,8 +4752,8 @@
       <xdr:row>121</xdr:row>
       <xdr:rowOff>153580</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="15" name="Ink 14">
@@ -4510,7 +4772,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="15" name="Ink 14">
@@ -4555,8 +4817,8 @@
       <xdr:row>121</xdr:row>
       <xdr:rowOff>44140</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="16" name="Ink 15">
@@ -4575,7 +4837,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="16" name="Ink 15">
@@ -4620,8 +4882,8 @@
       <xdr:row>121</xdr:row>
       <xdr:rowOff>155020</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="17" name="Ink 16">
@@ -4640,7 +4902,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="17" name="Ink 16">
@@ -4685,8 +4947,8 @@
       <xdr:row>120</xdr:row>
       <xdr:rowOff>206972</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="18" name="Ink 17">
@@ -4705,7 +4967,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="18" name="Ink 17">
@@ -4750,8 +5012,8 @@
       <xdr:row>133</xdr:row>
       <xdr:rowOff>27055</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="19" name="Ink 18">
@@ -4770,7 +5032,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="19" name="Ink 18">
@@ -4815,8 +5077,8 @@
       <xdr:row>134</xdr:row>
       <xdr:rowOff>39560</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="20" name="Ink 19">
@@ -4835,7 +5097,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="20" name="Ink 19">
@@ -4880,8 +5142,8 @@
       <xdr:row>134</xdr:row>
       <xdr:rowOff>202280</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="21" name="Ink 20">
@@ -4900,7 +5162,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="21" name="Ink 20">
@@ -4945,8 +5207,8 @@
       <xdr:row>135</xdr:row>
       <xdr:rowOff>180585</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId17">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="22" name="Ink 21">
@@ -4965,7 +5227,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="22" name="Ink 21">
@@ -5000,18 +5262,18 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>380650</xdr:colOff>
+      <xdr:colOff>523525</xdr:colOff>
       <xdr:row>136</xdr:row>
-      <xdr:rowOff>47272</xdr:rowOff>
+      <xdr:rowOff>47273</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>569830</xdr:colOff>
+      <xdr:colOff>712705</xdr:colOff>
       <xdr:row>136</xdr:row>
-      <xdr:rowOff>78592</xdr:rowOff>
+      <xdr:rowOff>78593</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="23" name="Ink 22">
@@ -5025,12 +5287,12 @@
           </xdr14:nvContentPartPr>
           <xdr14:nvPr macro=""/>
           <xdr14:xfrm>
-            <a:off x="9302400" y="28407960"/>
+            <a:off x="10953400" y="28407961"/>
             <a:ext cx="1903680" cy="31320"/>
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="23" name="Ink 22">
@@ -5075,8 +5337,8 @@
       <xdr:row>137</xdr:row>
       <xdr:rowOff>111257</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId21">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="24" name="Ink 23">
@@ -5095,7 +5357,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="24" name="Ink 23">
@@ -5140,8 +5402,8 @@
       <xdr:row>138</xdr:row>
       <xdr:rowOff>59682</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId23">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="25" name="Ink 24">
@@ -5160,7 +5422,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="25" name="Ink 24">
@@ -5205,8 +5467,8 @@
       <xdr:row>138</xdr:row>
       <xdr:rowOff>203322</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId25">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="26" name="Ink 25">
@@ -5225,7 +5487,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="26" name="Ink 25">
@@ -5270,8 +5532,8 @@
       <xdr:row>139</xdr:row>
       <xdr:rowOff>121130</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId27">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="27" name="Ink 26">
@@ -5290,7 +5552,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="27" name="Ink 26">
@@ -5335,8 +5597,8 @@
       <xdr:row>132</xdr:row>
       <xdr:rowOff>31127</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId29">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="28" name="Ink 27">
@@ -5355,7 +5617,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="28" name="Ink 27">
@@ -5400,8 +5662,8 @@
       <xdr:row>131</xdr:row>
       <xdr:rowOff>121582</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId31">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="29" name="Ink 28">
@@ -5420,7 +5682,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="29" name="Ink 28">
@@ -5456,17 +5718,17 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>331870</xdr:colOff>
-      <xdr:row>153</xdr:row>
+      <xdr:row>161</xdr:row>
       <xdr:rowOff>206437</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>734670</xdr:colOff>
-      <xdr:row>154</xdr:row>
+      <xdr:row>162</xdr:row>
       <xdr:rowOff>68445</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId33">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="30" name="Ink 29">
@@ -5485,7 +5747,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="30" name="Ink 29">
@@ -5521,17 +5783,17 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>467950</xdr:colOff>
-      <xdr:row>152</xdr:row>
+      <xdr:row>160</xdr:row>
       <xdr:rowOff>159012</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>121210</xdr:colOff>
-      <xdr:row>153</xdr:row>
+      <xdr:row>161</xdr:row>
       <xdr:rowOff>32917</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId35">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="31" name="Ink 30">
@@ -5550,7 +5812,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="31" name="Ink 30">
@@ -5586,17 +5848,17 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>564790</xdr:colOff>
-      <xdr:row>151</xdr:row>
+      <xdr:row>159</xdr:row>
       <xdr:rowOff>177845</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>754110</xdr:colOff>
-      <xdr:row>152</xdr:row>
+      <xdr:row>160</xdr:row>
       <xdr:rowOff>16092</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId37">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="32" name="Ink 31">
@@ -5615,7 +5877,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="32" name="Ink 31">
@@ -5651,17 +5913,17 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>224570</xdr:colOff>
-      <xdr:row>150</xdr:row>
+      <xdr:row>158</xdr:row>
       <xdr:rowOff>160660</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>230310</xdr:colOff>
-      <xdr:row>151</xdr:row>
+      <xdr:row>159</xdr:row>
       <xdr:rowOff>23045</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId39">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="33" name="Ink 32">
@@ -5680,7 +5942,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="33" name="Ink 32">
@@ -5716,17 +5978,17 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>370030</xdr:colOff>
-      <xdr:row>155</xdr:row>
+      <xdr:row>163</xdr:row>
       <xdr:rowOff>89590</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>555750</xdr:colOff>
-      <xdr:row>155</xdr:row>
+      <xdr:row>163</xdr:row>
       <xdr:rowOff>202990</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId41">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="34" name="Ink 33">
@@ -5745,7 +6007,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="34" name="Ink 33">
@@ -5781,17 +6043,17 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>435890</xdr:colOff>
-      <xdr:row>154</xdr:row>
+      <xdr:row>162</xdr:row>
       <xdr:rowOff>158085</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>699750</xdr:colOff>
-      <xdr:row>155</xdr:row>
+      <xdr:row>163</xdr:row>
       <xdr:rowOff>25150</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId43">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="35" name="Ink 34">
@@ -5810,7 +6072,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="35" name="Ink 34">
@@ -5846,17 +6108,17 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>463630</xdr:colOff>
-      <xdr:row>156</xdr:row>
+      <xdr:row>164</xdr:row>
       <xdr:rowOff>135917</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>517590</xdr:colOff>
-      <xdr:row>156</xdr:row>
+      <xdr:row>164</xdr:row>
       <xdr:rowOff>176597</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId45">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="36" name="Ink 35">
@@ -5875,7 +6137,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="36" name="Ink 35">
@@ -5911,17 +6173,17 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>773950</xdr:colOff>
-      <xdr:row>157</xdr:row>
+      <xdr:row>165</xdr:row>
       <xdr:rowOff>139422</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>469710</xdr:colOff>
-      <xdr:row>158</xdr:row>
+      <xdr:row>166</xdr:row>
       <xdr:rowOff>63367</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId47">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="37" name="Ink 36">
@@ -5940,7 +6202,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="37" name="Ink 36">
@@ -5976,17 +6238,17 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>55370</xdr:colOff>
-      <xdr:row>158</xdr:row>
+      <xdr:row>166</xdr:row>
       <xdr:rowOff>90367</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>199710</xdr:colOff>
-      <xdr:row>159</xdr:row>
+      <xdr:row>167</xdr:row>
       <xdr:rowOff>3495</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId49">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="38" name="Ink 37">
@@ -6005,7 +6267,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="38" name="Ink 37">
@@ -6041,17 +6303,17 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>299090</xdr:colOff>
-      <xdr:row>158</xdr:row>
+      <xdr:row>166</xdr:row>
       <xdr:rowOff>185767</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>274950</xdr:colOff>
-      <xdr:row>159</xdr:row>
+      <xdr:row>167</xdr:row>
       <xdr:rowOff>107535</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId51">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="39" name="Ink 38">
@@ -6070,7 +6332,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="39" name="Ink 38">
@@ -6106,17 +6368,17 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>226560</xdr:colOff>
-      <xdr:row>212</xdr:row>
+      <xdr:row>220</xdr:row>
       <xdr:rowOff>152080</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>485060</xdr:colOff>
-      <xdr:row>216</xdr:row>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>167560</xdr:colOff>
+      <xdr:row>224</xdr:row>
       <xdr:rowOff>165840</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId53">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="40" name="Ink 39">
@@ -6135,7 +6397,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="40" name="Ink 39">
@@ -6165,6 +6427,301 @@
         </xdr:pic>
       </mc:Fallback>
     </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>192087</xdr:colOff>
+      <xdr:row>142</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>1587</xdr:colOff>
+      <xdr:row>153</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="44" name="Group 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{117D0D35-BEA3-5249-90F5-39E313C48172}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="12193587" y="29640213"/>
+          <a:ext cx="4000500" cy="2297112"/>
+          <a:chOff x="7804150" y="23285450"/>
+          <a:chExt cx="4000500" cy="2286000"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="45" name="Donut 44">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0413C040-A2E2-BD9C-87F2-7DEAE9928FDC}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="7804150" y="23310850"/>
+            <a:ext cx="2413000" cy="2260600"/>
+          </a:xfrm>
+          <a:prstGeom prst="donut">
+            <a:avLst>
+              <a:gd name="adj" fmla="val 1880"/>
+            </a:avLst>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="46" name="Donut 45">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B4DC7FB-BA49-AAB1-A4C5-E8BFBF3966BA}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="9391650" y="23285450"/>
+            <a:ext cx="2413000" cy="2260600"/>
+          </a:xfrm>
+          <a:prstGeom prst="donut">
+            <a:avLst>
+              <a:gd name="adj" fmla="val 1880"/>
+            </a:avLst>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>285525</xdr:colOff>
+      <xdr:row>142</xdr:row>
+      <xdr:rowOff>184187</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>306945</xdr:colOff>
+      <xdr:row>152</xdr:row>
+      <xdr:rowOff>39905</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId55">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="47" name="Ink 46">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B5052ED-D0A2-921E-26E5-1A4B25107ABD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="10715400" y="29799000"/>
+            <a:ext cx="1735920" cy="1943280"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="47" name="Ink 46">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B5052ED-D0A2-921E-26E5-1A4B25107ABD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId56"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10661400" y="29691360"/>
+              <a:ext cx="1843560" cy="2158920"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>241300</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>26359</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D59D374-03FF-192C-034A-65EAC3520809}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1155700" y="20523200"/>
+          <a:ext cx="7772400" cy="1448759"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>130</xdr:row>
+      <xdr:rowOff>77235</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5548F6CC-4AB3-2FEE-9611-3DCAADAB0E02}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5581650" y="25228550"/>
+          <a:ext cx="5708650" cy="1264685"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -6947,7 +7504,35 @@
       <inkml:brushProperty name="color" value="#CC0066"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 767 24575,'19'1'0,"35"13"0,11 0 0,22 5 0,16 2 0,7-3-1093,-32-8 1,8 0 0,6-2 0,4 1-1,3-1 1,0 0 0,-2 1 0,-3-1-1,-6 2 880,1 1 0,-4 0 0,-2 1 0,-2 0 1,2-1-1,3 0 0,5-2 213,3-1 0,10-1 0,6-1 0,1 0 0,0-1 0,-6 0 0,-9-2 0,-11 0 0,-17-1 1318,21-2 0,-15-1-1318,26-3 0,-14 0 1744,-42-1-1744,-24 1 0,22-9 0,24 5 0,21 1 0,-4 0 0,0-3 0,2 2 0,-11 2 0,10-1 0,-1 2 0,-7 2 3111,21 1 0,-5 4-3111,-24 1 0,0 0 0,7 2 0,11 2 0,9 2 0,0 0 0,-10-1 76,-15-2 0,-7-1 1,4 1-77,30 3 0,4 1 0,-27-4 0,-34-6 0,-5 2 0,-21-1 0,-4 0 490,0-1-490,-5-1 0,2 0 0,2-9 0,-6-7 0,0-7 0,-6-1 0,-18-28 0,-7-12 0,-3-1 0,-7-6 0,-11-9 0,-10-7 0,5 6 0,4 0 0,-2 6 0,2 17 0,-5 0 0,10 12 0,-3 0 0,-14-13 0,40 37 0,9 7 0,47 32 0,11 15 0,28 21 0,-19-7 0,4 7 0,9 16 0,3 5 0,-22-22 0,2 0 0,-1 2 0,3 4 0,0 2 0,1 0-264,0-1 0,1 1 0,2-1 264,4 4 0,3 1 0,-2-3 0,-5-7 0,-1-1 0,-3-2 0,18 20 0,-10-9 0,-6-3 0,-37-18 0,-4-18 0,-13-11 792,-4-9-792,-6-2 0,-8 3 0,-53 28 0,6 6 0,-10 8 0,9-5 0,-6 4 0,-3 2 0,5-2 0,-5 2 0,1 1 0,3-2 0,-8 5 0,4-2 0,0 1 0,-8 6 0,-1 0 0,14-8 0,23-17 0,6-4 0,-32 29 0,72-53 0,1-2 0,0 2 0,0 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 779 24575,'19'1'0,"35"13"0,11 0 0,22 6 0,17 1 0,6-3-1093,-32-7 1,8-1 0,6-2 0,4 1-1,3-1 1,1 0 0,-3 1 0,-3-1-1,-6 3 880,1 0 0,-4 0 0,-1 1 0,-3 0 1,2 0-1,3-1 0,5-2 213,3-1 0,10-1 0,7-1 0,0 0 0,0-1 0,-6 0 0,-9-2 0,-11 1 0,-16-2 1318,20-2 0,-15-1-1318,26-4 0,-14 1 1744,-42-1-1744,-24 1 0,22-9 0,24 5 0,22 1 0,-5 0 0,0-3 0,2 1 0,-11 3 0,10-1 0,-1 2 0,-7 2 3111,22 1 0,-6 4-3111,-24 1 0,0 0 0,7 2 0,11 2 0,9 3 0,1-1 0,-11-1 76,-15-2 0,-7-1 1,4 1-77,30 3 0,4 1 0,-26-4 0,-35-6 0,-5 2 0,-21 0 0,-4-1 490,0-1-490,-5-1 0,2-1 0,2-8 0,-6-7 0,0-7 0,-6-2 0,-18-28 0,-7-12 0,-3-1 0,-7-6 0,-12-9 0,-9-7 0,5 5 0,4 1 0,-2 6 0,2 17 0,-5 0 0,10 12 0,-3 1 0,-14-14 0,40 37 0,9 8 0,47 32 0,11 16 0,28 21 0,-19-8 0,4 8 0,9 16 0,3 5 0,-22-22 0,2 0 0,0 2 0,2 4 0,0 2 0,1-1-264,0 0 0,1 1 0,2-1 264,4 4 0,3 1 0,-2-3 0,-5-7 0,0-1 0,-4-2 0,18 20 0,-10-9 0,-6-4 0,-37-17 0,-4-19 0,-13-10 792,-4-10-792,-6-2 0,-8 3 0,-53 28 0,6 7 0,-10 7 0,8-4 0,-5 4 0,-3 2 0,5-3 0,-5 3 0,1 1 0,3-3 0,-8 6 0,4-2 0,-1 1 0,-7 6 0,-1-1 0,14-7 0,23-17 0,6-5 0,-32 30 0,72-54 0,1-2 0,0 2 0,0 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink35.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-22T15:52:52.123"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.3" units="cm"/>
+      <inkml:brushProperty name="height" value="0.6" units="cm"/>
+      <inkml:brushProperty name="color" value="#FFFC00"/>
+      <inkml:brushProperty name="tip" value="rectangle"/>
+      <inkml:brushProperty name="rasterOp" value="maskPen"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">4730 484,'-41'1,"1"5,13 16,-18 14,-4 3,5-4,14-8,17-17,1 7,3-5,1-1,-20 26,0-7,-11 16,14-15,5 3,7-5,-7 5,1 2,-23 22,8 15,-8 4,20-10,1 2,-11 21,2 2,-1 2,13-35,-1-4,-7 10,1-4,4 15,0-36,11-10,-1-6,5-10,-5 14,7-9,-1-2,5-3,-3-2,3 10,-2-7,4 7,8 21,0 30,3-5,-7-1,-2-38,0-2,3-4,5 20,-2-24,0 23,-7-31,2 14,-1-13,14 51,9 20,-15-33,1 0,18 43,-16-46,1-17,-8-15,-1-8,3 7,5-3,0 4,-1-5,-2-7,14 45,-12-13,20 50,-26-47,5-3,-9-23,-4 15,5 6,-4 9,4-13,-5-11,-17 69,14-2,2 7,-8-9,1 1,6 17,4-14,0-35,15-12,-6-34,11 13,-12-16,1 4,10-4,0 12,8 15,-2 1,-11 13,0-19,-9-5,-2-6,2-4,2 5,2 7,-2-8,4 4,-1-12,6-1,-3-2,4-6,-3 3,-3-2,17 2,-18 0,14 2,-14 3,6 3,-7 2,3 1,2 2,14 7,-6-7,4 3,-23-11,-5 19,5 52,5 7,2-4,1-2,3-7,-2 7,-19-75,-1-2,-23-7,16 6,-19-4,6 13,-24 0,-33 13,7-5,-6 0,7 1,2-1,1 1,4-2,-17 5,61-13,5-2,5 2,0-1,-23 7,15-5,-24 5,18-9,-12 0,8-4,4 0,3 0,13 0,-26 0,-12 8,0-2,2 6,24-5,11-4,1-1,-17-2,15 0,-12 0,16 0,-4 0,-4-5,-34-7,23 4,-30-10,4 1,-9-1,-30-4,-6-1,9 0,-1 0,19 8,-3 2,13 1,-13-3,8-1,2 1,-9 2,21 6,1 0,-22 0,15-5,39 2,-50-36,-4 5,18 5,2 0,-12-1,24 3,27 19,-8-9,-18-17,-11 5,-16-22,3 22,9-3,2 0,29 24,-8-21,19 23,-41-53,17 33,-5-14,-2-2,-16-4,20 11,1 0,-7 0,10 3,15 14,-10-29,-4-5,-15-13,-6-7,19 22,1 1,-16-17,0-1,7 10,3 4,10 11,0 1,-3 0,2 1,-13-29,27 43,8 3,8 18,0 0,1-18,0-32,0-14,9 3,2-2,-3 23,0-1,4-25,2 0,4 19,-1 2,-3 1,2-1,11-10,3 2,-7 17,2 0,9-14,2-2,2 1,0 3,-7 16,-1 0,2-6,0 0,18-26,-19 31,2-1,0 3,0-1,5-9,1 2,25-23,-4-5,-16 30,-5 1,-11 11,13-7,0 1,19-5,-1 4,-16 14,4-2,19-17,0-1,-12 16,1 1,27-20,-2 4,4 9,-26 18,0 1,11-6,6 1,-14-5,3-4,-7 6,0 0,7-5,-1 1,-8 5,-1 4,38 0,-3 2,12 12,-47 7,3 3,34 6,8 1,0-6,5 1,-3 6,5 3,-9-3,-10-5,-7-1,4 4,-15 2,-35-2,-4 3,-7 4,6 5,-7-5,2 2,-9-8,3 1,-59 22,-4-3,-8 2,-13 5,-10 4,10-7,-10 4,-1 2,4-1,-9 10,5 2,-3-2,15-10,-4 0,3 0,4-1,3 4,4-1,2-1,-22 14,3-3,19-14,1 0,-6 10,4-2,-3 4,33-15,8-14,-21 41,17-21,-7 16,31-28,4-21,62 1,-12-11,8-6,8-4,9-4,3-7,-6-6,4-6,1-3,-3-1,-3 4,-1-2,-1-1,-2-3,1-6,0-5,-4 1,-5 4,-3 6,-5 2,-7 3,-3-6,-7 6,5 3,-40 27,-58 25,-53 29,-2 3,34-15,-1 2,-4 2,-5 4,15-7,-6 3,-2 3,-3 0,0 2,2 0,2 1,-10 5,1 2,1 0,2 1,2 0,4 1,-1 2,4 0,2 0,3 2,3 1,-12 13,3 4,5-3,10-7,-4 6,13-6,13-2,16-15,23-39,5-2,60-33,32-24,-30 19,4-3,12-11,-23 11,9-7,7-5,4-4,3-2,0-1,-3 1,-4 3,-6 3,5-4,-5 2,-3 1,-1 0,2-1,3-3,5-3,5-4,4-2,-2 0,-4 2,-9 3,-10 7,5-14,-13 6,-14 13,-8 10,-90 101,13-9,-9 12,-6 7,4-10,-5 5,-3 4,-3 3,-1 4,17-18,-2 3,-1 3,-1 2,0 0,1 0,2-2,2-3,-6 9,3-2,1-1,1-1,1-1,1 1,-10 10,-1 3,3-2,6-6,13-12,-1 12,24-21,29-36,23-49,13-25,-1 10,5-4,4-5,3-8,3-7,2-2,1 0,2 1,1 0,2-1,3-4,-12 12,3-5,2-2,-2 2,-3 3,-6 8,8-9,-6 7,0 0,20-21,1-1,-39 46,-62 74,-13 22,-12 20,-1 3,15-20,0 2,-1 1,-1 4,0-1,-3 5,0 2,2-4,3-6,-2 8,3-6,6-7,0 6,15-29,14-40,39-75,-11 32,4-5,4-7,4-5,-3 3,0 0,-3 4,3-3,-11 26,-44 105,-3-15,-5 12,-5 5,-2 4,-4 5,-2 5,-1 1,3-5,-1 5,0 1,0-3,2-6,0-5,2-5,1-3,2-2,-11 21,3-3,27-44,41-67,13-24,2-15,4-13,-6 15,6-8,1-4,-3 3,-5 3,-1-1,-1 1,-1 2,7-13,-2 3,-3 7,2-9,-14 34,-27 51,-21 48,-21 37,-2 0,6-11,-1 0,-6 7,2-5,-6 9,-3 2,3-4,6-12,4-7,5-8,-1-2,-11 16,-1-1,24-43,28-47,28-45,9-18,-8 1,1-5,2 9,4-4,-7 7,-3-8,-14 34,-33 112,-17 48,12-47,-2 2,-2 8,1-4,-1 10,-1 2,1-2,4-9,0 7,4-8,2-6,-3 12,13-34,43-93,-10-4,2-12,2-11,3-11,-1 8,5 2,-3 6,-5-11,-9 32,-15 74,-17 52,-7 17,6-24,1 0,-6 22,5-11,10-34,19-70,12-33,7-16,-5 10,2-4,0 2,11-23,-3 4,-2 8,-8 16,-21 40,-24 79,-12 17,-12 11,2-13,62-123,15-30,-15 21,2-2,4-1,4-4,-4 10,16-11,-50 110,-11 33,-1 10,-3 9,0-6,-2 6,0-8,-1-3,0-15,-4-11,27-122,9-39,-3 11,1-1,3-7,0 8,3 5,-11 62,-6 24,26 22,16-5,4 2,18 17,-16-18,-6-5,-26-12,-10-26,-4-9,8-26,-7 22,2-3,-6 31,1 3</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -8238,6 +8823,1775 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{054011AF-5510-824C-BC72-0F4577571645}">
+  <dimension ref="B2:K182"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="5.83203125" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>725</v>
+      </c>
+      <c r="C6" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>727</v>
+      </c>
+      <c r="E9" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>729</v>
+      </c>
+      <c r="G10" t="s">
+        <v>585</v>
+      </c>
+      <c r="H10" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>730</v>
+      </c>
+      <c r="G11" t="s">
+        <v>734</v>
+      </c>
+      <c r="H11" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="E12" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="E13" t="s">
+        <v>732</v>
+      </c>
+      <c r="G13" t="s">
+        <v>723</v>
+      </c>
+      <c r="H13" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="E14" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="G15">
+        <v>150000</v>
+      </c>
+      <c r="H15">
+        <v>375202</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="G16">
+        <f>G15*H15</f>
+        <v>56280300000</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="G17">
+        <v>200</v>
+      </c>
+      <c r="H17">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B18">
+        <v>9</v>
+      </c>
+      <c r="G18">
+        <f>G17*H17</f>
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="D28">
+        <v>2</v>
+      </c>
+      <c r="E28" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="D29">
+        <v>2</v>
+      </c>
+      <c r="E29" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="D30">
+        <v>2</v>
+      </c>
+      <c r="E30" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="D32">
+        <v>3</v>
+      </c>
+      <c r="E32" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="33" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D33">
+        <v>3</v>
+      </c>
+      <c r="E33" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="34" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D34">
+        <v>3</v>
+      </c>
+      <c r="E34" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="35" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D35">
+        <v>3</v>
+      </c>
+      <c r="E35" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="36" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D36">
+        <v>3</v>
+      </c>
+      <c r="E36" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="37" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D37">
+        <v>3</v>
+      </c>
+      <c r="E37" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="38" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D38">
+        <v>3</v>
+      </c>
+      <c r="E38" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="39" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D39">
+        <v>3</v>
+      </c>
+      <c r="E39" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="40" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D40">
+        <v>3</v>
+      </c>
+      <c r="E40" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="41" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="E41" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="45" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D45" t="s">
+        <v>188</v>
+      </c>
+      <c r="F45" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="48" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D48" t="s">
+        <v>188</v>
+      </c>
+      <c r="F48" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="50" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="D50" t="s">
+        <v>641</v>
+      </c>
+      <c r="E50" s="119" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="51" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="D51" t="s">
+        <v>736</v>
+      </c>
+      <c r="E51" s="119"/>
+    </row>
+    <row r="52" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="D52" t="s">
+        <v>737</v>
+      </c>
+      <c r="E52" s="119"/>
+    </row>
+    <row r="53" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="D53" t="s">
+        <v>738</v>
+      </c>
+      <c r="E53" s="119"/>
+    </row>
+    <row r="56" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C56" t="s">
+        <v>675</v>
+      </c>
+      <c r="G56" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="57" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C57" t="s">
+        <v>740</v>
+      </c>
+      <c r="D57" t="s">
+        <v>741</v>
+      </c>
+      <c r="E57" t="s">
+        <v>742</v>
+      </c>
+      <c r="G57" t="s">
+        <v>740</v>
+      </c>
+      <c r="H57" t="s">
+        <v>741</v>
+      </c>
+      <c r="I57" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="58" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="D58" t="s">
+        <v>611</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+      <c r="H58" t="s">
+        <v>611</v>
+      </c>
+      <c r="I58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C59">
+        <v>2</v>
+      </c>
+      <c r="D59" t="s">
+        <v>645</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="G59">
+        <v>2</v>
+      </c>
+      <c r="H59" t="s">
+        <v>645</v>
+      </c>
+      <c r="I59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C60">
+        <v>3</v>
+      </c>
+      <c r="D60" t="s">
+        <v>646</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
+      </c>
+      <c r="G60">
+        <v>3</v>
+      </c>
+      <c r="H60" t="s">
+        <v>646</v>
+      </c>
+      <c r="I60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C61">
+        <v>4</v>
+      </c>
+      <c r="D61" t="s">
+        <v>647</v>
+      </c>
+      <c r="E61">
+        <v>2</v>
+      </c>
+      <c r="G61">
+        <v>4</v>
+      </c>
+      <c r="H61" t="s">
+        <v>647</v>
+      </c>
+      <c r="I61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C62">
+        <v>5</v>
+      </c>
+      <c r="D62" t="s">
+        <v>648</v>
+      </c>
+      <c r="E62">
+        <v>2</v>
+      </c>
+      <c r="G62">
+        <v>5</v>
+      </c>
+      <c r="H62" t="s">
+        <v>648</v>
+      </c>
+      <c r="I62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C66" t="s">
+        <v>675</v>
+      </c>
+      <c r="F66" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="67" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C67" t="s">
+        <v>740</v>
+      </c>
+      <c r="D67" t="s">
+        <v>741</v>
+      </c>
+      <c r="E67" t="s">
+        <v>742</v>
+      </c>
+      <c r="F67" t="s">
+        <v>740</v>
+      </c>
+      <c r="G67" t="s">
+        <v>741</v>
+      </c>
+      <c r="H67" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="68" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C68" s="1">
+        <v>1</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="E68" s="1">
+        <v>1</v>
+      </c>
+      <c r="F68" s="1">
+        <v>1</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="H68" s="1">
+        <v>1</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="K68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C69" s="120">
+        <v>1</v>
+      </c>
+      <c r="D69" s="120" t="s">
+        <v>611</v>
+      </c>
+      <c r="E69" s="120">
+        <v>1</v>
+      </c>
+      <c r="F69" s="120">
+        <v>2</v>
+      </c>
+      <c r="G69" s="120" t="s">
+        <v>645</v>
+      </c>
+      <c r="H69" s="120">
+        <v>1</v>
+      </c>
+      <c r="J69" s="120" t="s">
+        <v>744</v>
+      </c>
+      <c r="K69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C70" s="120">
+        <v>1</v>
+      </c>
+      <c r="D70" s="120" t="s">
+        <v>611</v>
+      </c>
+      <c r="E70" s="120">
+        <v>1</v>
+      </c>
+      <c r="F70" s="120">
+        <v>3</v>
+      </c>
+      <c r="G70" s="120" t="s">
+        <v>646</v>
+      </c>
+      <c r="H70" s="120">
+        <v>1</v>
+      </c>
+      <c r="J70" s="120" t="s">
+        <v>745</v>
+      </c>
+      <c r="K70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C71" s="1">
+        <v>2</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="E71" s="1">
+        <v>1</v>
+      </c>
+      <c r="F71" s="1">
+        <v>1</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="H71" s="1">
+        <v>1</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="K71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C72" s="1">
+        <v>2</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="E72" s="1">
+        <v>1</v>
+      </c>
+      <c r="F72" s="1">
+        <v>2</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="H72" s="1">
+        <v>1</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="K72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C73" s="120">
+        <v>2</v>
+      </c>
+      <c r="D73" s="120" t="s">
+        <v>645</v>
+      </c>
+      <c r="E73" s="120">
+        <v>1</v>
+      </c>
+      <c r="F73" s="120">
+        <v>3</v>
+      </c>
+      <c r="G73" s="120" t="s">
+        <v>646</v>
+      </c>
+      <c r="H73" s="120">
+        <v>1</v>
+      </c>
+      <c r="J73" s="120" t="s">
+        <v>748</v>
+      </c>
+      <c r="K73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C74" s="1">
+        <v>3</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="E74" s="1">
+        <v>1</v>
+      </c>
+      <c r="F74" s="1">
+        <v>1</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="H74" s="1">
+        <v>1</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="K74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C75" s="1">
+        <v>3</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="E75" s="1">
+        <v>1</v>
+      </c>
+      <c r="F75" s="1">
+        <v>2</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="H75" s="1">
+        <v>1</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="K75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C76" s="1">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="E76" s="1">
+        <v>1</v>
+      </c>
+      <c r="F76" s="1">
+        <v>3</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="H76" s="1">
+        <v>1</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="K76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C77" s="1">
+        <v>4</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="E77" s="1">
+        <v>2</v>
+      </c>
+      <c r="F77" s="1">
+        <v>4</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="H77" s="1">
+        <v>2</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="K77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C78" s="120">
+        <v>4</v>
+      </c>
+      <c r="D78" s="120" t="s">
+        <v>647</v>
+      </c>
+      <c r="E78" s="120">
+        <v>2</v>
+      </c>
+      <c r="F78" s="120">
+        <v>5</v>
+      </c>
+      <c r="G78" s="120" t="s">
+        <v>648</v>
+      </c>
+      <c r="H78" s="120">
+        <v>2</v>
+      </c>
+      <c r="J78" s="120" t="s">
+        <v>753</v>
+      </c>
+      <c r="K78">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C79" s="1">
+        <v>5</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="E79" s="1">
+        <v>2</v>
+      </c>
+      <c r="F79" s="1">
+        <v>4</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="H79" s="1">
+        <v>2</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="K79">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C80" s="1">
+        <v>5</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="E80" s="1">
+        <v>2</v>
+      </c>
+      <c r="F80" s="1">
+        <v>5</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="H80" s="1">
+        <v>2</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="K80">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C86" t="s">
+        <v>675</v>
+      </c>
+      <c r="G86" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C87" t="s">
+        <v>740</v>
+      </c>
+      <c r="D87" t="s">
+        <v>741</v>
+      </c>
+      <c r="E87" t="s">
+        <v>742</v>
+      </c>
+      <c r="G87" t="s">
+        <v>740</v>
+      </c>
+      <c r="H87" t="s">
+        <v>741</v>
+      </c>
+      <c r="I87" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C88">
+        <v>1</v>
+      </c>
+      <c r="D88" t="s">
+        <v>611</v>
+      </c>
+      <c r="E88">
+        <v>1</v>
+      </c>
+      <c r="G88">
+        <v>1</v>
+      </c>
+      <c r="H88" t="s">
+        <v>611</v>
+      </c>
+      <c r="I88">
+        <v>1</v>
+      </c>
+      <c r="K88" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C89">
+        <v>2</v>
+      </c>
+      <c r="D89" t="s">
+        <v>645</v>
+      </c>
+      <c r="E89">
+        <v>1</v>
+      </c>
+      <c r="G89">
+        <v>2</v>
+      </c>
+      <c r="H89" t="s">
+        <v>645</v>
+      </c>
+      <c r="I89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C90">
+        <v>3</v>
+      </c>
+      <c r="D90" t="s">
+        <v>646</v>
+      </c>
+      <c r="E90">
+        <v>1</v>
+      </c>
+      <c r="G90">
+        <v>3</v>
+      </c>
+      <c r="H90" t="s">
+        <v>646</v>
+      </c>
+      <c r="I90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C91">
+        <v>4</v>
+      </c>
+      <c r="D91" t="s">
+        <v>647</v>
+      </c>
+      <c r="E91">
+        <v>2</v>
+      </c>
+      <c r="G91">
+        <v>4</v>
+      </c>
+      <c r="H91" t="s">
+        <v>647</v>
+      </c>
+      <c r="I91">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C92">
+        <v>5</v>
+      </c>
+      <c r="D92" t="s">
+        <v>648</v>
+      </c>
+      <c r="E92">
+        <v>2</v>
+      </c>
+      <c r="G92">
+        <v>5</v>
+      </c>
+      <c r="H92" t="s">
+        <v>648</v>
+      </c>
+      <c r="I92">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C94" t="s">
+        <v>675</v>
+      </c>
+      <c r="F94" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C95" t="s">
+        <v>740</v>
+      </c>
+      <c r="D95" t="s">
+        <v>741</v>
+      </c>
+      <c r="E95" t="s">
+        <v>742</v>
+      </c>
+      <c r="F95" t="s">
+        <v>740</v>
+      </c>
+      <c r="G95" t="s">
+        <v>741</v>
+      </c>
+      <c r="H95" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C96">
+        <v>1</v>
+      </c>
+      <c r="D96" t="s">
+        <v>611</v>
+      </c>
+      <c r="E96">
+        <v>1</v>
+      </c>
+      <c r="F96">
+        <v>2</v>
+      </c>
+      <c r="G96" t="s">
+        <v>645</v>
+      </c>
+      <c r="H96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C97">
+        <v>1</v>
+      </c>
+      <c r="D97" t="s">
+        <v>611</v>
+      </c>
+      <c r="E97">
+        <v>1</v>
+      </c>
+      <c r="F97">
+        <v>3</v>
+      </c>
+      <c r="G97" t="s">
+        <v>646</v>
+      </c>
+      <c r="H97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C98">
+        <v>2</v>
+      </c>
+      <c r="D98" t="s">
+        <v>645</v>
+      </c>
+      <c r="E98">
+        <v>1</v>
+      </c>
+      <c r="F98">
+        <v>3</v>
+      </c>
+      <c r="G98" t="s">
+        <v>646</v>
+      </c>
+      <c r="H98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C99">
+        <v>4</v>
+      </c>
+      <c r="D99" t="s">
+        <v>647</v>
+      </c>
+      <c r="E99">
+        <v>2</v>
+      </c>
+      <c r="F99">
+        <v>5</v>
+      </c>
+      <c r="G99" t="s">
+        <v>648</v>
+      </c>
+      <c r="H99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="D111" t="s">
+        <v>757</v>
+      </c>
+      <c r="E111" t="s">
+        <v>758</v>
+      </c>
+      <c r="H111" t="s">
+        <v>759</v>
+      </c>
+      <c r="I111" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="112" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="D112" t="s">
+        <v>740</v>
+      </c>
+      <c r="E112" t="s">
+        <v>761</v>
+      </c>
+      <c r="H112" t="s">
+        <v>740</v>
+      </c>
+      <c r="I112" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="113" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="D113" t="s">
+        <v>761</v>
+      </c>
+      <c r="E113" t="s">
+        <v>762</v>
+      </c>
+      <c r="H113" t="s">
+        <v>761</v>
+      </c>
+      <c r="I113" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="116" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C116" t="s">
+        <v>757</v>
+      </c>
+      <c r="F116" t="s">
+        <v>740</v>
+      </c>
+      <c r="G116" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="117" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C117" t="s">
+        <v>763</v>
+      </c>
+      <c r="F117" t="s">
+        <v>740</v>
+      </c>
+      <c r="G117" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="118" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C118" t="s">
+        <v>759</v>
+      </c>
+      <c r="F118" t="s">
+        <v>740</v>
+      </c>
+      <c r="G118" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="119" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C119" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="121" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="D121" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="122" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="D122" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="123" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="D123" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="126" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C126" t="s">
+        <v>675</v>
+      </c>
+      <c r="F126" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="127" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C127" t="s">
+        <v>740</v>
+      </c>
+      <c r="D127" t="s">
+        <v>761</v>
+      </c>
+      <c r="F127" t="s">
+        <v>761</v>
+      </c>
+      <c r="G127" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="128" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C128">
+        <v>1</v>
+      </c>
+      <c r="D128">
+        <v>1</v>
+      </c>
+      <c r="F128">
+        <v>1</v>
+      </c>
+      <c r="G128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C129">
+        <v>2</v>
+      </c>
+      <c r="D129">
+        <v>1</v>
+      </c>
+      <c r="F129">
+        <v>2</v>
+      </c>
+      <c r="G129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C130">
+        <v>3</v>
+      </c>
+      <c r="D130">
+        <v>2</v>
+      </c>
+      <c r="F130">
+        <v>3</v>
+      </c>
+      <c r="G130">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C131">
+        <v>4</v>
+      </c>
+      <c r="D131">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C132">
+        <v>5</v>
+      </c>
+      <c r="D132">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="134" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C134" t="s">
+        <v>768</v>
+      </c>
+      <c r="E134" t="s">
+        <v>769</v>
+      </c>
+      <c r="H134" t="s">
+        <v>770</v>
+      </c>
+      <c r="J134" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="135" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C135" t="s">
+        <v>740</v>
+      </c>
+      <c r="D135" t="s">
+        <v>761</v>
+      </c>
+      <c r="E135" t="s">
+        <v>761</v>
+      </c>
+      <c r="F135" t="s">
+        <v>762</v>
+      </c>
+      <c r="H135" t="s">
+        <v>740</v>
+      </c>
+      <c r="I135" t="s">
+        <v>761</v>
+      </c>
+      <c r="J135" t="s">
+        <v>761</v>
+      </c>
+      <c r="K135" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="136" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C136">
+        <v>1</v>
+      </c>
+      <c r="D136">
+        <v>1</v>
+      </c>
+      <c r="E136">
+        <v>1</v>
+      </c>
+      <c r="F136">
+        <v>1</v>
+      </c>
+      <c r="H136">
+        <v>1</v>
+      </c>
+      <c r="I136">
+        <v>1</v>
+      </c>
+      <c r="J136">
+        <v>1</v>
+      </c>
+      <c r="K136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C137">
+        <v>2</v>
+      </c>
+      <c r="D137">
+        <v>1</v>
+      </c>
+      <c r="E137">
+        <v>1</v>
+      </c>
+      <c r="F137">
+        <v>1</v>
+      </c>
+      <c r="H137">
+        <v>2</v>
+      </c>
+      <c r="I137">
+        <v>1</v>
+      </c>
+      <c r="J137">
+        <v>1</v>
+      </c>
+      <c r="K137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C138">
+        <v>3</v>
+      </c>
+      <c r="D138">
+        <v>2</v>
+      </c>
+      <c r="E138">
+        <v>2</v>
+      </c>
+      <c r="F138">
+        <v>1</v>
+      </c>
+      <c r="H138">
+        <v>3</v>
+      </c>
+      <c r="I138">
+        <v>2</v>
+      </c>
+      <c r="J138">
+        <v>2</v>
+      </c>
+      <c r="K138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C139">
+        <v>4</v>
+      </c>
+      <c r="D139">
+        <v>2</v>
+      </c>
+      <c r="E139">
+        <v>2</v>
+      </c>
+      <c r="F139">
+        <v>1</v>
+      </c>
+      <c r="H139">
+        <v>4</v>
+      </c>
+      <c r="I139">
+        <v>2</v>
+      </c>
+      <c r="J139">
+        <v>2</v>
+      </c>
+      <c r="K139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C140">
+        <v>5</v>
+      </c>
+      <c r="D140">
+        <v>3</v>
+      </c>
+      <c r="E140">
+        <v>3</v>
+      </c>
+      <c r="F140">
+        <v>2</v>
+      </c>
+      <c r="H140">
+        <v>5</v>
+      </c>
+      <c r="I140">
+        <v>3</v>
+      </c>
+      <c r="J140">
+        <v>3</v>
+      </c>
+      <c r="K140">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C143" t="s">
+        <v>768</v>
+      </c>
+      <c r="E143" t="s">
+        <v>769</v>
+      </c>
+      <c r="G143" t="s">
+        <v>770</v>
+      </c>
+      <c r="I143" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="144" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C144" t="s">
+        <v>740</v>
+      </c>
+      <c r="D144" t="s">
+        <v>761</v>
+      </c>
+      <c r="E144" t="s">
+        <v>761</v>
+      </c>
+      <c r="F144" t="s">
+        <v>762</v>
+      </c>
+      <c r="G144" t="s">
+        <v>740</v>
+      </c>
+      <c r="H144" t="s">
+        <v>761</v>
+      </c>
+      <c r="I144" t="s">
+        <v>761</v>
+      </c>
+      <c r="J144" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="145" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C145">
+        <v>1</v>
+      </c>
+      <c r="D145">
+        <v>1</v>
+      </c>
+      <c r="E145" s="1">
+        <v>1</v>
+      </c>
+      <c r="F145">
+        <v>1</v>
+      </c>
+      <c r="G145">
+        <v>2</v>
+      </c>
+      <c r="H145">
+        <v>1</v>
+      </c>
+      <c r="I145" s="1">
+        <v>1</v>
+      </c>
+      <c r="J145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C146">
+        <v>3</v>
+      </c>
+      <c r="D146">
+        <v>2</v>
+      </c>
+      <c r="E146" s="1">
+        <v>2</v>
+      </c>
+      <c r="F146">
+        <v>1</v>
+      </c>
+      <c r="G146">
+        <v>4</v>
+      </c>
+      <c r="H146">
+        <v>2</v>
+      </c>
+      <c r="I146" s="1">
+        <v>2</v>
+      </c>
+      <c r="J146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C158" t="s">
+        <v>768</v>
+      </c>
+      <c r="G158" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="159" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C159" t="s">
+        <v>740</v>
+      </c>
+      <c r="D159" t="s">
+        <v>761</v>
+      </c>
+      <c r="G159" t="s">
+        <v>740</v>
+      </c>
+      <c r="H159" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="160" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C160" s="1">
+        <v>1</v>
+      </c>
+      <c r="D160" s="1">
+        <v>1</v>
+      </c>
+      <c r="G160" s="31">
+        <v>1</v>
+      </c>
+      <c r="H160" s="31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C161" s="1">
+        <v>2</v>
+      </c>
+      <c r="D161" s="1">
+        <v>1</v>
+      </c>
+      <c r="G161" s="31">
+        <v>2</v>
+      </c>
+      <c r="H161" s="31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C162" s="1">
+        <v>3</v>
+      </c>
+      <c r="D162" s="1">
+        <v>2</v>
+      </c>
+      <c r="G162" s="31">
+        <v>3</v>
+      </c>
+      <c r="H162" s="31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="163" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C163" s="1">
+        <v>4</v>
+      </c>
+      <c r="D163" s="1">
+        <v>2</v>
+      </c>
+      <c r="G163" s="31">
+        <v>5</v>
+      </c>
+      <c r="H163" s="31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C164" s="1">
+        <v>5</v>
+      </c>
+      <c r="D164" s="1">
+        <v>3</v>
+      </c>
+      <c r="G164" s="31">
+        <v>6</v>
+      </c>
+      <c r="H164" s="31">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="166" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C166" s="119" t="s">
+        <v>726</v>
+      </c>
+      <c r="D166" s="119"/>
+      <c r="G166" s="119" t="s">
+        <v>588</v>
+      </c>
+      <c r="H166" s="119"/>
+    </row>
+    <row r="167" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C167" s="1">
+        <v>1</v>
+      </c>
+      <c r="D167" s="1">
+        <v>1</v>
+      </c>
+      <c r="G167" s="1">
+        <v>1</v>
+      </c>
+      <c r="H167" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C168" s="1">
+        <v>2</v>
+      </c>
+      <c r="D168" s="1">
+        <v>1</v>
+      </c>
+      <c r="G168" s="1">
+        <v>2</v>
+      </c>
+      <c r="H168" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C169" s="1">
+        <v>3</v>
+      </c>
+      <c r="D169" s="1">
+        <v>2</v>
+      </c>
+      <c r="G169" s="1">
+        <v>3</v>
+      </c>
+      <c r="H169" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="170" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C170" s="1">
+        <v>4</v>
+      </c>
+      <c r="D170" s="1">
+        <v>2</v>
+      </c>
+      <c r="G170" s="1">
+        <v>4</v>
+      </c>
+      <c r="H170" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="171" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C171" s="1">
+        <v>5</v>
+      </c>
+      <c r="D171" s="1">
+        <v>3</v>
+      </c>
+      <c r="G171" s="1">
+        <v>5</v>
+      </c>
+      <c r="H171" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="172" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C172" s="31">
+        <v>1</v>
+      </c>
+      <c r="D172" s="31">
+        <v>1</v>
+      </c>
+      <c r="G172" s="31">
+        <v>5</v>
+      </c>
+      <c r="H172" s="31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="173" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C173" s="31">
+        <v>2</v>
+      </c>
+      <c r="D173" s="31">
+        <v>1</v>
+      </c>
+      <c r="G173" s="31">
+        <v>6</v>
+      </c>
+      <c r="H173" s="31">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="174" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C174" s="31">
+        <v>3</v>
+      </c>
+      <c r="D174" s="31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="175" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C175" s="31">
+        <v>5</v>
+      </c>
+      <c r="D175" s="31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C176" s="31">
+        <v>6</v>
+      </c>
+      <c r="D176" s="31">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="180" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C180" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="181" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="E181" t="s">
+        <v>757</v>
+      </c>
+      <c r="H181" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="182" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="E182" t="s">
+        <v>289</v>
+      </c>
+      <c r="H182" t="s">
+        <v>292</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="E50:E53"/>
+    <mergeCell ref="C166:D166"/>
+    <mergeCell ref="G166:H166"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C30BBE9F-6251-054D-8156-7574F8262F96}">
   <dimension ref="B2:M88"/>
@@ -10818,7 +13172,7 @@
       </c>
       <c r="J56" t="str">
         <f ca="1">TEXT(NOW(),"YYYY-MM-DD")</f>
-        <v>2026-08-21</v>
+        <v>2026-08-23</v>
       </c>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.2">
@@ -10827,7 +13181,7 @@
       </c>
       <c r="J57" t="str">
         <f ca="1">TEXT(NOW(),"dddd, mmm DD yyyy")</f>
-        <v>Friday, Aug 21 2026</v>
+        <v>Sunday, Aug 23 2026</v>
       </c>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.2">
@@ -13527,327 +15881,329 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A260109-2701-BC4B-AB2B-1617AC20DBFF}">
-  <dimension ref="B2:R239"/>
+  <dimension ref="B2:R299"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" customWidth="1"/>
+    <col min="4" max="4" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.1640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="4.6640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="4.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="109" t="s">
         <v>585</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="G2" s="41" t="s">
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="G2" s="109" t="s">
         <v>586</v>
       </c>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
+      <c r="H2" s="109"/>
+      <c r="I2" s="109"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B3" s="42"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="44"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="53"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="43"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="51"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B4" s="45"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="47"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="56"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="45"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="54"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B5" s="45"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="47"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="56"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="45"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="54"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B6" s="45"/>
-      <c r="C6" s="46"/>
-      <c r="D6" s="46"/>
-      <c r="E6" s="47"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="56"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="45"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="54"/>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B7" s="45"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="47"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="56"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="45"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="54"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B8" s="45"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="47"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="55"/>
-      <c r="I8" s="56"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="45"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="54"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B9" s="45"/>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="47"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="56"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="45"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="54"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B10" s="45"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="47"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="55"/>
-      <c r="I10" s="56"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="45"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="53"/>
+      <c r="I10" s="54"/>
     </row>
     <row r="11" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="48"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="50"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="55"/>
-      <c r="I11" s="56"/>
+      <c r="B11" s="46"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="48"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="53"/>
+      <c r="I11" s="54"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="G12" s="54"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="56"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="54"/>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="G13" s="54"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="56"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="53"/>
+      <c r="I13" s="54"/>
     </row>
     <row r="14" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="G14" s="57"/>
-      <c r="H14" s="58"/>
-      <c r="I14" s="59"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="57"/>
     </row>
     <row r="16" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="17" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B17" s="42"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="52"/>
-      <c r="H17" s="53"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="49"/>
+      <c r="G17" s="50"/>
+      <c r="H17" s="51"/>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B18" s="45"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="55"/>
-      <c r="H18" s="56"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="52"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="54"/>
     </row>
     <row r="19" spans="2:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="45"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="55"/>
-      <c r="H19" s="56"/>
+      <c r="B19" s="44"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="52"/>
+      <c r="G19" s="53"/>
+      <c r="H19" s="54"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B20" s="45"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="55"/>
-      <c r="H20" s="56"/>
-      <c r="J20" s="75" t="s">
+      <c r="B20" s="44"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="52"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="54"/>
+      <c r="J20" s="110" t="s">
         <v>587</v>
       </c>
-      <c r="K20" s="76"/>
-      <c r="L20" s="76"/>
-      <c r="M20" s="77"/>
+      <c r="K20" s="111"/>
+      <c r="L20" s="111"/>
+      <c r="M20" s="112"/>
       <c r="O20" t="s">
         <v>590</v>
       </c>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B21" s="45"/>
-      <c r="C21" s="46"/>
-      <c r="D21" s="46"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="55"/>
-      <c r="H21" s="56"/>
-      <c r="J21" s="78"/>
-      <c r="K21" s="79"/>
-      <c r="L21" s="79"/>
-      <c r="M21" s="80"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="52"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="54"/>
+      <c r="J21" s="113"/>
+      <c r="K21" s="114"/>
+      <c r="L21" s="114"/>
+      <c r="M21" s="115"/>
       <c r="P21" t="s">
         <v>592</v>
       </c>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B22" s="45"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="55"/>
-      <c r="H22" s="56"/>
-      <c r="J22" s="78"/>
-      <c r="K22" s="79"/>
-      <c r="L22" s="79"/>
-      <c r="M22" s="80"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="52"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="54"/>
+      <c r="J22" s="113"/>
+      <c r="K22" s="114"/>
+      <c r="L22" s="114"/>
+      <c r="M22" s="115"/>
       <c r="Q22" t="s">
         <v>594</v>
       </c>
     </row>
     <row r="23" spans="2:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="45"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="55"/>
-      <c r="H23" s="56"/>
-      <c r="J23" s="81"/>
-      <c r="K23" s="82"/>
-      <c r="L23" s="82"/>
-      <c r="M23" s="83"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="52"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="54"/>
+      <c r="J23" s="116"/>
+      <c r="K23" s="117"/>
+      <c r="L23" s="117"/>
+      <c r="M23" s="118"/>
       <c r="P23" t="s">
         <v>593</v>
       </c>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B24" s="45"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="55"/>
-      <c r="H24" s="56"/>
-      <c r="J24" s="66" t="s">
+      <c r="B24" s="44"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="52"/>
+      <c r="G24" s="53"/>
+      <c r="H24" s="54"/>
+      <c r="J24" s="94" t="s">
         <v>589</v>
       </c>
-      <c r="K24" s="67"/>
-      <c r="L24" s="67"/>
-      <c r="M24" s="68"/>
+      <c r="K24" s="95"/>
+      <c r="L24" s="95"/>
+      <c r="M24" s="96"/>
       <c r="O24" t="s">
         <v>591</v>
       </c>
     </row>
     <row r="25" spans="2:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="48"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="50"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="55"/>
-      <c r="H25" s="56"/>
-      <c r="J25" s="69"/>
-      <c r="K25" s="70"/>
-      <c r="L25" s="70"/>
-      <c r="M25" s="71"/>
+      <c r="B25" s="46"/>
+      <c r="C25" s="47"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="52"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="54"/>
+      <c r="J25" s="97"/>
+      <c r="K25" s="98"/>
+      <c r="L25" s="98"/>
+      <c r="M25" s="99"/>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="F26" s="54"/>
-      <c r="G26" s="55"/>
-      <c r="H26" s="56"/>
-      <c r="J26" s="69"/>
-      <c r="K26" s="70"/>
-      <c r="L26" s="70"/>
-      <c r="M26" s="71"/>
+      <c r="F26" s="52"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="54"/>
+      <c r="J26" s="97"/>
+      <c r="K26" s="98"/>
+      <c r="L26" s="98"/>
+      <c r="M26" s="99"/>
     </row>
     <row r="27" spans="2:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="F27" s="54"/>
-      <c r="G27" s="55"/>
-      <c r="H27" s="56"/>
-      <c r="J27" s="72"/>
-      <c r="K27" s="73"/>
-      <c r="L27" s="73"/>
-      <c r="M27" s="74"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="54"/>
+      <c r="J27" s="100"/>
+      <c r="K27" s="101"/>
+      <c r="L27" s="101"/>
+      <c r="M27" s="102"/>
       <c r="O27" t="s">
         <v>595</v>
       </c>
     </row>
     <row r="28" spans="2:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="F28" s="57"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="59"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="57"/>
       <c r="O28" t="s">
         <v>596</v>
       </c>
     </row>
     <row r="32" spans="2:17" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="33" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B33" s="42" t="s">
+      <c r="B33" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="C33" s="43" t="s">
+      <c r="C33" s="42" t="s">
         <v>105</v>
       </c>
-      <c r="D33" s="43" t="s">
+      <c r="D33" s="42" t="s">
         <v>103</v>
       </c>
-      <c r="E33" s="44" t="s">
+      <c r="E33" s="43" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="34" spans="2:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="45"/>
-      <c r="C34" s="46"/>
-      <c r="D34" s="46"/>
-      <c r="E34" s="47"/>
+      <c r="B34" s="44"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="45"/>
       <c r="O34" t="s">
         <v>597</v>
       </c>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B35" s="45"/>
-      <c r="C35" s="46"/>
-      <c r="D35" s="46"/>
-      <c r="E35" s="47"/>
-      <c r="J35" s="75" t="s">
+      <c r="B35" s="44"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="45"/>
+      <c r="J35" s="110" t="s">
         <v>588</v>
       </c>
-      <c r="K35" s="76"/>
-      <c r="L35" s="76"/>
-      <c r="M35" s="77"/>
+      <c r="K35" s="111"/>
+      <c r="L35" s="111"/>
+      <c r="M35" s="112"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B36" s="45"/>
-      <c r="C36" s="46"/>
-      <c r="D36" s="46"/>
-      <c r="E36" s="47"/>
-      <c r="J36" s="78"/>
-      <c r="K36" s="79"/>
-      <c r="L36" s="79"/>
-      <c r="M36" s="80"/>
+      <c r="B36" s="44"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="45"/>
+      <c r="J36" s="113"/>
+      <c r="K36" s="114"/>
+      <c r="L36" s="114"/>
+      <c r="M36" s="115"/>
       <c r="O36" t="s">
         <v>598</v>
       </c>
@@ -13856,14 +16212,14 @@
       </c>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B37" s="45"/>
-      <c r="C37" s="46"/>
-      <c r="D37" s="46"/>
-      <c r="E37" s="47"/>
-      <c r="J37" s="78"/>
-      <c r="K37" s="79"/>
-      <c r="L37" s="79"/>
-      <c r="M37" s="80"/>
+      <c r="B37" s="44"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="45"/>
+      <c r="J37" s="113"/>
+      <c r="K37" s="114"/>
+      <c r="L37" s="114"/>
+      <c r="M37" s="115"/>
       <c r="O37" t="s">
         <v>599</v>
       </c>
@@ -13872,26 +16228,26 @@
       </c>
     </row>
     <row r="38" spans="2:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="45"/>
-      <c r="C38" s="46"/>
-      <c r="D38" s="46"/>
-      <c r="E38" s="47"/>
-      <c r="J38" s="81"/>
-      <c r="K38" s="82"/>
-      <c r="L38" s="82"/>
-      <c r="M38" s="83"/>
+      <c r="B38" s="44"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="45"/>
+      <c r="J38" s="116"/>
+      <c r="K38" s="117"/>
+      <c r="L38" s="117"/>
+      <c r="M38" s="118"/>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B39" s="45"/>
-      <c r="C39" s="46"/>
-      <c r="D39" s="46"/>
-      <c r="E39" s="47"/>
-      <c r="J39" s="66" t="s">
+      <c r="B39" s="44"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="45"/>
+      <c r="J39" s="94" t="s">
         <v>600</v>
       </c>
-      <c r="K39" s="67"/>
-      <c r="L39" s="67"/>
-      <c r="M39" s="68"/>
+      <c r="K39" s="95"/>
+      <c r="L39" s="95"/>
+      <c r="M39" s="96"/>
       <c r="O39" t="s">
         <v>598</v>
       </c>
@@ -13906,14 +16262,14 @@
       </c>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B40" s="45"/>
-      <c r="C40" s="46"/>
-      <c r="D40" s="46"/>
-      <c r="E40" s="47"/>
-      <c r="J40" s="69"/>
-      <c r="K40" s="70"/>
-      <c r="L40" s="70"/>
-      <c r="M40" s="71"/>
+      <c r="B40" s="44"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="45"/>
+      <c r="J40" s="97"/>
+      <c r="K40" s="98"/>
+      <c r="L40" s="98"/>
+      <c r="M40" s="99"/>
       <c r="O40" t="s">
         <v>599</v>
       </c>
@@ -13928,130 +16284,130 @@
       </c>
     </row>
     <row r="41" spans="2:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="48"/>
-      <c r="C41" s="49"/>
-      <c r="D41" s="49"/>
-      <c r="E41" s="50"/>
-      <c r="J41" s="69"/>
-      <c r="K41" s="70"/>
-      <c r="L41" s="70"/>
-      <c r="M41" s="71"/>
+      <c r="B41" s="46"/>
+      <c r="C41" s="47"/>
+      <c r="D41" s="47"/>
+      <c r="E41" s="48"/>
+      <c r="J41" s="97"/>
+      <c r="K41" s="98"/>
+      <c r="L41" s="98"/>
+      <c r="M41" s="99"/>
     </row>
     <row r="42" spans="2:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="51" t="s">
+      <c r="B42" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="C42" s="52" t="s">
+      <c r="C42" s="50" t="s">
         <v>105</v>
       </c>
-      <c r="D42" s="53" t="s">
+      <c r="D42" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="E42" s="85" t="s">
+      <c r="E42" s="59" t="s">
         <v>602</v>
       </c>
-      <c r="J42" s="72"/>
-      <c r="K42" s="73"/>
-      <c r="L42" s="73"/>
-      <c r="M42" s="74"/>
+      <c r="J42" s="100"/>
+      <c r="K42" s="101"/>
+      <c r="L42" s="101"/>
+      <c r="M42" s="102"/>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B43" s="54"/>
-      <c r="C43" s="55"/>
-      <c r="D43" s="56"/>
-      <c r="E43" s="86"/>
-      <c r="J43" s="66" t="s">
+      <c r="B43" s="52"/>
+      <c r="C43" s="53"/>
+      <c r="D43" s="54"/>
+      <c r="E43" s="60"/>
+      <c r="J43" s="94" t="s">
         <v>601</v>
       </c>
-      <c r="K43" s="67"/>
-      <c r="L43" s="67"/>
-      <c r="M43" s="68"/>
+      <c r="K43" s="95"/>
+      <c r="L43" s="95"/>
+      <c r="M43" s="96"/>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B44" s="54"/>
-      <c r="C44" s="55"/>
-      <c r="D44" s="56"/>
-      <c r="E44" s="86"/>
-      <c r="J44" s="69"/>
-      <c r="K44" s="70"/>
-      <c r="L44" s="70"/>
-      <c r="M44" s="71"/>
+      <c r="B44" s="52"/>
+      <c r="C44" s="53"/>
+      <c r="D44" s="54"/>
+      <c r="E44" s="60"/>
+      <c r="J44" s="97"/>
+      <c r="K44" s="98"/>
+      <c r="L44" s="98"/>
+      <c r="M44" s="99"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B45" s="54"/>
-      <c r="C45" s="55"/>
-      <c r="D45" s="56"/>
-      <c r="E45" s="86"/>
-      <c r="J45" s="69"/>
-      <c r="K45" s="70"/>
-      <c r="L45" s="70"/>
-      <c r="M45" s="71"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="53"/>
+      <c r="D45" s="54"/>
+      <c r="E45" s="60"/>
+      <c r="J45" s="97"/>
+      <c r="K45" s="98"/>
+      <c r="L45" s="98"/>
+      <c r="M45" s="99"/>
     </row>
     <row r="46" spans="2:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="54"/>
-      <c r="C46" s="55"/>
-      <c r="D46" s="56"/>
-      <c r="E46" s="86"/>
-      <c r="J46" s="72"/>
-      <c r="K46" s="73"/>
-      <c r="L46" s="73"/>
-      <c r="M46" s="74"/>
+      <c r="B46" s="52"/>
+      <c r="C46" s="53"/>
+      <c r="D46" s="54"/>
+      <c r="E46" s="60"/>
+      <c r="J46" s="100"/>
+      <c r="K46" s="101"/>
+      <c r="L46" s="101"/>
+      <c r="M46" s="102"/>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B47" s="54"/>
-      <c r="C47" s="55"/>
-      <c r="D47" s="56"/>
-      <c r="E47" s="86"/>
+      <c r="B47" s="52"/>
+      <c r="C47" s="53"/>
+      <c r="D47" s="54"/>
+      <c r="E47" s="60"/>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B48" s="54"/>
-      <c r="C48" s="55"/>
-      <c r="D48" s="56"/>
-      <c r="E48" s="86"/>
+      <c r="B48" s="52"/>
+      <c r="C48" s="53"/>
+      <c r="D48" s="54"/>
+      <c r="E48" s="60"/>
     </row>
     <row r="49" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B49" s="54"/>
-      <c r="C49" s="55"/>
-      <c r="D49" s="56"/>
-      <c r="E49" s="86"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="53"/>
+      <c r="D49" s="54"/>
+      <c r="E49" s="60"/>
     </row>
     <row r="50" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B50" s="54"/>
-      <c r="C50" s="55"/>
-      <c r="D50" s="56"/>
-      <c r="E50" s="86"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="53"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="60"/>
     </row>
     <row r="51" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B51" s="54"/>
-      <c r="C51" s="55"/>
-      <c r="D51" s="56"/>
-      <c r="E51" s="86"/>
+      <c r="B51" s="52"/>
+      <c r="C51" s="53"/>
+      <c r="D51" s="54"/>
+      <c r="E51" s="60"/>
     </row>
     <row r="52" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B52" s="54"/>
-      <c r="C52" s="55"/>
-      <c r="D52" s="56"/>
-      <c r="E52" s="86"/>
+      <c r="B52" s="52"/>
+      <c r="C52" s="53"/>
+      <c r="D52" s="54"/>
+      <c r="E52" s="60"/>
     </row>
     <row r="53" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="57"/>
-      <c r="C53" s="58"/>
-      <c r="D53" s="59"/>
-      <c r="E53" s="87"/>
-    </row>
-    <row r="57" spans="2:16" s="88" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B57" s="88" t="s">
+      <c r="B53" s="55"/>
+      <c r="C53" s="56"/>
+      <c r="D53" s="57"/>
+      <c r="E53" s="61"/>
+    </row>
+    <row r="57" spans="2:16" s="62" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B57" s="62" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="58" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="59" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="E59" s="60" t="s">
+      <c r="E59" s="103" t="s">
         <v>608</v>
       </c>
-      <c r="F59" s="61"/>
-      <c r="G59" s="61"/>
-      <c r="H59" s="62"/>
+      <c r="F59" s="104"/>
+      <c r="G59" s="104"/>
+      <c r="H59" s="105"/>
       <c r="J59" t="s">
         <v>609</v>
       </c>
@@ -14060,10 +16416,10 @@
       <c r="B60" t="s">
         <v>604</v>
       </c>
-      <c r="E60" s="63"/>
-      <c r="F60" s="64"/>
-      <c r="G60" s="64"/>
-      <c r="H60" s="65"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="108"/>
     </row>
     <row r="61" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
@@ -14137,8 +16493,6 @@
       <c r="E64" s="5" t="s">
         <v>630</v>
       </c>
-      <c r="F64" s="89"/>
-      <c r="G64" s="89"/>
       <c r="H64" s="6" t="s">
         <v>635</v>
       </c>
@@ -14153,8 +16507,6 @@
       <c r="E65" s="5" t="s">
         <v>631</v>
       </c>
-      <c r="F65" s="89"/>
-      <c r="G65" s="89"/>
       <c r="H65" s="6" t="s">
         <v>636</v>
       </c>
@@ -14169,8 +16521,6 @@
       <c r="E66" s="5" t="s">
         <v>632</v>
       </c>
-      <c r="F66" s="89"/>
-      <c r="G66" s="89"/>
       <c r="H66" s="6" t="s">
         <v>637</v>
       </c>
@@ -14188,8 +16538,6 @@
       <c r="E67" s="5" t="s">
         <v>633</v>
       </c>
-      <c r="F67" s="89"/>
-      <c r="G67" s="89"/>
       <c r="H67" s="6" t="s">
         <v>638</v>
       </c>
@@ -14287,8 +16635,6 @@
       <c r="E80" s="5" t="s">
         <v>630</v>
       </c>
-      <c r="F80" s="89"/>
-      <c r="G80" s="89"/>
       <c r="H80" s="6" t="s">
         <v>635</v>
       </c>
@@ -14297,8 +16643,6 @@
       <c r="E81" s="5" t="s">
         <v>639</v>
       </c>
-      <c r="F81" s="89"/>
-      <c r="G81" s="89"/>
       <c r="H81" s="6" t="s">
         <v>636</v>
       </c>
@@ -14318,7 +16662,7 @@
       </c>
     </row>
     <row r="87" spans="4:9" x14ac:dyDescent="0.2">
-      <c r="E87" s="84" t="s">
+      <c r="E87" s="58" t="s">
         <v>630</v>
       </c>
     </row>
@@ -14326,22 +16670,22 @@
       <c r="D88" t="s">
         <v>311</v>
       </c>
-      <c r="E88" s="84" t="s">
+      <c r="E88" s="58" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="89" spans="4:9" x14ac:dyDescent="0.2">
-      <c r="E89" s="90" t="s">
+      <c r="E89" s="58" t="s">
         <v>632</v>
       </c>
     </row>
     <row r="90" spans="4:9" x14ac:dyDescent="0.2">
-      <c r="E90" s="90" t="s">
+      <c r="E90" s="58" t="s">
         <v>633</v>
       </c>
     </row>
     <row r="91" spans="4:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E91" s="91" t="s">
+      <c r="E91" s="22" t="s">
         <v>639</v>
       </c>
     </row>
@@ -14352,12 +16696,12 @@
       </c>
     </row>
     <row r="94" spans="4:9" x14ac:dyDescent="0.2">
-      <c r="H94" s="84" t="s">
+      <c r="H94" s="58" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="95" spans="4:9" x14ac:dyDescent="0.2">
-      <c r="H95" s="84" t="s">
+      <c r="H95" s="58" t="s">
         <v>636</v>
       </c>
       <c r="I95" t="s">
@@ -14365,17 +16709,17 @@
       </c>
     </row>
     <row r="96" spans="4:9" x14ac:dyDescent="0.2">
-      <c r="H96" s="84" t="s">
+      <c r="H96" s="58" t="s">
         <v>637</v>
       </c>
     </row>
     <row r="97" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="H97" s="84" t="s">
+      <c r="H97" s="58" t="s">
         <v>638</v>
       </c>
     </row>
     <row r="98" spans="3:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="H98" s="91" t="s">
+      <c r="H98" s="22" t="s">
         <v>639</v>
       </c>
     </row>
@@ -14539,72 +16883,72 @@
       </c>
     </row>
     <row r="116" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C116" s="101">
+      <c r="C116" s="72">
         <v>2</v>
       </c>
-      <c r="D116" s="102" t="s">
+      <c r="D116" s="73" t="s">
         <v>646</v>
       </c>
-      <c r="E116" s="102">
+      <c r="E116" s="73">
         <v>2</v>
       </c>
-      <c r="F116" s="103" t="s">
+      <c r="F116" s="74" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="117" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C117" s="107">
+      <c r="C117" s="78">
         <v>2</v>
       </c>
-      <c r="D117" s="108" t="s">
+      <c r="D117" s="79" t="s">
         <v>646</v>
       </c>
-      <c r="E117" s="108">
+      <c r="E117" s="79">
         <v>2</v>
       </c>
-      <c r="F117" s="109" t="s">
+      <c r="F117" s="80" t="s">
         <v>653</v>
       </c>
     </row>
     <row r="118" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C118" s="104">
+      <c r="C118" s="75">
         <v>2</v>
       </c>
-      <c r="D118" s="105" t="s">
+      <c r="D118" s="76" t="s">
         <v>646</v>
       </c>
-      <c r="E118" s="105">
+      <c r="E118" s="76">
         <v>2</v>
       </c>
-      <c r="F118" s="106" t="s">
+      <c r="F118" s="77" t="s">
         <v>654</v>
       </c>
     </row>
     <row r="119" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C119" s="101">
+      <c r="C119" s="72">
         <v>2</v>
       </c>
-      <c r="D119" s="102" t="s">
+      <c r="D119" s="73" t="s">
         <v>647</v>
       </c>
-      <c r="E119" s="102">
+      <c r="E119" s="73">
         <v>2</v>
       </c>
-      <c r="F119" s="103" t="s">
+      <c r="F119" s="74" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="120" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C120" s="107">
+      <c r="C120" s="78">
         <v>2</v>
       </c>
-      <c r="D120" s="108" t="s">
+      <c r="D120" s="79" t="s">
         <v>647</v>
       </c>
-      <c r="E120" s="108">
+      <c r="E120" s="79">
         <v>2</v>
       </c>
-      <c r="F120" s="109" t="s">
+      <c r="F120" s="80" t="s">
         <v>653</v>
       </c>
       <c r="H120" t="s">
@@ -14612,16 +16956,16 @@
       </c>
     </row>
     <row r="121" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C121" s="104">
+      <c r="C121" s="75">
         <v>2</v>
       </c>
-      <c r="D121" s="105" t="s">
+      <c r="D121" s="76" t="s">
         <v>647</v>
       </c>
-      <c r="E121" s="105">
+      <c r="E121" s="76">
         <v>2</v>
       </c>
-      <c r="F121" s="106" t="s">
+      <c r="F121" s="77" t="s">
         <v>654</v>
       </c>
       <c r="H121" t="s">
@@ -14629,86 +16973,86 @@
       </c>
     </row>
     <row r="122" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C122" s="101">
+      <c r="C122" s="72">
         <v>3</v>
       </c>
-      <c r="D122" s="102" t="s">
+      <c r="D122" s="73" t="s">
         <v>648</v>
       </c>
-      <c r="E122" s="102">
+      <c r="E122" s="73">
         <v>3</v>
       </c>
-      <c r="F122" s="103" t="s">
+      <c r="F122" s="74" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="123" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C123" s="104">
+      <c r="C123" s="75">
         <v>3</v>
       </c>
-      <c r="D123" s="105" t="s">
+      <c r="D123" s="76" t="s">
         <v>648</v>
       </c>
-      <c r="E123" s="105">
+      <c r="E123" s="76">
         <v>3</v>
       </c>
-      <c r="F123" s="106" t="s">
+      <c r="F123" s="77" t="s">
         <v>655</v>
       </c>
     </row>
     <row r="124" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C124" s="101">
+      <c r="C124" s="72">
         <v>3</v>
       </c>
-      <c r="D124" s="102" t="s">
+      <c r="D124" s="73" t="s">
         <v>649</v>
       </c>
-      <c r="E124" s="102">
+      <c r="E124" s="73">
         <v>3</v>
       </c>
-      <c r="F124" s="103" t="s">
+      <c r="F124" s="74" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="125" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C125" s="104">
+      <c r="C125" s="75">
         <v>3</v>
       </c>
-      <c r="D125" s="105" t="s">
+      <c r="D125" s="76" t="s">
         <v>649</v>
       </c>
-      <c r="E125" s="105">
+      <c r="E125" s="76">
         <v>3</v>
       </c>
-      <c r="F125" s="106" t="s">
+      <c r="F125" s="77" t="s">
         <v>655</v>
       </c>
     </row>
     <row r="126" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C126" s="107">
+      <c r="C126" s="78">
         <v>3</v>
       </c>
-      <c r="D126" s="108" t="s">
+      <c r="D126" s="79" t="s">
         <v>650</v>
       </c>
-      <c r="E126" s="108">
+      <c r="E126" s="79">
         <v>3</v>
       </c>
-      <c r="F126" s="109" t="s">
+      <c r="F126" s="80" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="127" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C127" s="104">
+      <c r="C127" s="75">
         <v>3</v>
       </c>
-      <c r="D127" s="105" t="s">
+      <c r="D127" s="76" t="s">
         <v>650</v>
       </c>
-      <c r="E127" s="105">
+      <c r="E127" s="76">
         <v>3</v>
       </c>
-      <c r="F127" s="106" t="s">
+      <c r="F127" s="77" t="s">
         <v>655</v>
       </c>
     </row>
@@ -14735,72 +17079,72 @@
       </c>
     </row>
     <row r="132" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C132" s="110">
+      <c r="C132" s="81">
         <v>1</v>
       </c>
-      <c r="D132" s="111" t="s">
+      <c r="D132" s="82" t="s">
         <v>611</v>
       </c>
-      <c r="E132" s="111" t="s">
+      <c r="E132" s="82" t="s">
         <v>157</v>
       </c>
-      <c r="F132" s="112" t="s">
+      <c r="F132" s="83" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="133" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C133" s="113">
+      <c r="C133" s="84">
         <v>1</v>
       </c>
-      <c r="D133" s="114" t="s">
+      <c r="D133" s="85" t="s">
         <v>645</v>
       </c>
-      <c r="E133" s="114" t="s">
+      <c r="E133" s="85" t="s">
         <v>157</v>
       </c>
-      <c r="F133" s="115" t="s">
+      <c r="F133" s="86" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="134" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C134" s="101">
+      <c r="C134" s="72">
         <v>2</v>
       </c>
-      <c r="D134" s="102" t="s">
+      <c r="D134" s="73" t="s">
         <v>646</v>
       </c>
-      <c r="E134" s="102">
+      <c r="E134" s="73">
         <v>2</v>
       </c>
-      <c r="F134" s="103" t="s">
+      <c r="F134" s="74" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="135" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C135" s="107">
+      <c r="C135" s="78">
         <v>2</v>
       </c>
-      <c r="D135" s="108" t="s">
+      <c r="D135" s="79" t="s">
         <v>646</v>
       </c>
-      <c r="E135" s="108">
+      <c r="E135" s="79">
         <v>2</v>
       </c>
-      <c r="F135" s="109" t="s">
+      <c r="F135" s="80" t="s">
         <v>653</v>
       </c>
     </row>
     <row r="136" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C136" s="104">
+      <c r="C136" s="75">
         <v>2</v>
       </c>
-      <c r="D136" s="105" t="s">
+      <c r="D136" s="76" t="s">
         <v>646</v>
       </c>
-      <c r="E136" s="105">
+      <c r="E136" s="76">
         <v>2</v>
       </c>
-      <c r="F136" s="106" t="s">
+      <c r="F136" s="77" t="s">
         <v>654</v>
       </c>
       <c r="H136" t="s">
@@ -14808,16 +17152,16 @@
       </c>
     </row>
     <row r="137" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C137" s="101">
+      <c r="C137" s="72">
         <v>2</v>
       </c>
-      <c r="D137" s="102" t="s">
+      <c r="D137" s="73" t="s">
         <v>647</v>
       </c>
-      <c r="E137" s="102">
+      <c r="E137" s="73">
         <v>2</v>
       </c>
-      <c r="F137" s="103" t="s">
+      <c r="F137" s="74" t="s">
         <v>652</v>
       </c>
       <c r="H137" t="s">
@@ -14825,16 +17169,16 @@
       </c>
     </row>
     <row r="138" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C138" s="107">
+      <c r="C138" s="78">
         <v>2</v>
       </c>
-      <c r="D138" s="108" t="s">
+      <c r="D138" s="79" t="s">
         <v>647</v>
       </c>
-      <c r="E138" s="108">
+      <c r="E138" s="79">
         <v>2</v>
       </c>
-      <c r="F138" s="109" t="s">
+      <c r="F138" s="80" t="s">
         <v>653</v>
       </c>
       <c r="H138" t="s">
@@ -14842,16 +17186,16 @@
       </c>
     </row>
     <row r="139" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C139" s="104">
+      <c r="C139" s="75">
         <v>2</v>
       </c>
-      <c r="D139" s="105" t="s">
+      <c r="D139" s="76" t="s">
         <v>647</v>
       </c>
-      <c r="E139" s="105">
+      <c r="E139" s="76">
         <v>2</v>
       </c>
-      <c r="F139" s="106" t="s">
+      <c r="F139" s="77" t="s">
         <v>654</v>
       </c>
       <c r="H139" t="s">
@@ -14859,899 +17203,1205 @@
       </c>
     </row>
     <row r="140" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C140" s="101">
+      <c r="C140" s="72">
         <v>3</v>
       </c>
-      <c r="D140" s="102" t="s">
+      <c r="D140" s="73" t="s">
         <v>648</v>
       </c>
-      <c r="E140" s="102">
+      <c r="E140" s="73">
         <v>3</v>
       </c>
-      <c r="F140" s="103" t="s">
+      <c r="F140" s="74" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="141" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C141" s="104">
+      <c r="C141" s="75">
         <v>3</v>
       </c>
-      <c r="D141" s="105" t="s">
+      <c r="D141" s="76" t="s">
         <v>648</v>
       </c>
-      <c r="E141" s="105">
+      <c r="E141" s="76">
         <v>3</v>
       </c>
-      <c r="F141" s="106" t="s">
+      <c r="F141" s="77" t="s">
         <v>655</v>
       </c>
     </row>
     <row r="142" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C142" s="101">
+      <c r="C142" s="72">
         <v>3</v>
       </c>
-      <c r="D142" s="102" t="s">
+      <c r="D142" s="73" t="s">
         <v>649</v>
       </c>
-      <c r="E142" s="102">
+      <c r="E142" s="73">
         <v>3</v>
       </c>
-      <c r="F142" s="103" t="s">
+      <c r="F142" s="74" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="143" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C143" s="104">
+      <c r="C143" s="75">
         <v>3</v>
       </c>
-      <c r="D143" s="105" t="s">
+      <c r="D143" s="76" t="s">
         <v>649</v>
       </c>
-      <c r="E143" s="105">
+      <c r="E143" s="76">
         <v>3</v>
       </c>
-      <c r="F143" s="106" t="s">
+      <c r="F143" s="77" t="s">
         <v>655</v>
       </c>
     </row>
     <row r="144" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C144" s="107">
+      <c r="C144" s="78">
         <v>3</v>
       </c>
-      <c r="D144" s="108" t="s">
+      <c r="D144" s="79" t="s">
         <v>650</v>
       </c>
-      <c r="E144" s="108">
+      <c r="E144" s="79">
         <v>3</v>
       </c>
-      <c r="F144" s="109" t="s">
+      <c r="F144" s="80" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="145" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C145" s="104">
+    <row r="145" spans="3:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C145" s="75">
         <v>3</v>
       </c>
-      <c r="D145" s="105" t="s">
+      <c r="D145" s="76" t="s">
         <v>650</v>
       </c>
-      <c r="E145" s="105">
+      <c r="E145" s="76">
         <v>3</v>
       </c>
-      <c r="F145" s="106" t="s">
+      <c r="F145" s="77" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="146" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C146" s="116">
+    <row r="146" spans="3:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C146" s="87">
         <v>4</v>
       </c>
-      <c r="D146" s="117" t="s">
+      <c r="D146" s="88" t="s">
         <v>651</v>
       </c>
-      <c r="E146" s="117" t="s">
+      <c r="E146" s="88" t="s">
         <v>157</v>
       </c>
-      <c r="F146" s="118" t="s">
+      <c r="F146" s="89" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="149" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C149" t="s">
+    <row r="157" spans="3:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C157" t="s">
         <v>642</v>
       </c>
-      <c r="E149" t="s">
+      <c r="E157" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="150" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C150" s="14" t="s">
+    <row r="158" spans="3:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C158" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="D150" s="15" t="s">
+      <c r="D158" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="E150" s="15" t="s">
+      <c r="E158" s="15" t="s">
         <v>277</v>
       </c>
-      <c r="F150" s="16" t="s">
+      <c r="F158" s="16" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="151" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C151" s="101">
+    <row r="159" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C159" s="72">
         <v>2</v>
       </c>
-      <c r="D151" s="102" t="s">
+      <c r="D159" s="73" t="s">
         <v>646</v>
       </c>
-      <c r="E151" s="102">
+      <c r="E159" s="73">
         <v>2</v>
       </c>
-      <c r="F151" s="103" t="s">
+      <c r="F159" s="74" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="152" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C152" s="104">
+    <row r="160" spans="3:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C160" s="75">
         <v>2</v>
       </c>
-      <c r="D152" s="105" t="s">
+      <c r="D160" s="76" t="s">
         <v>647</v>
       </c>
-      <c r="E152" s="105">
+      <c r="E160" s="76">
         <v>2</v>
       </c>
-      <c r="F152" s="106" t="s">
+      <c r="F160" s="77" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="153" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C153" s="101">
+    <row r="161" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C161" s="72">
         <v>2</v>
       </c>
-      <c r="D153" s="102" t="s">
+      <c r="D161" s="73" t="s">
         <v>646</v>
       </c>
-      <c r="E153" s="102">
+      <c r="E161" s="73">
         <v>2</v>
       </c>
-      <c r="F153" s="103" t="s">
+      <c r="F161" s="74" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="154" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C154" s="104">
+    <row r="162" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C162" s="75">
         <v>2</v>
       </c>
-      <c r="D154" s="105" t="s">
+      <c r="D162" s="76" t="s">
         <v>647</v>
       </c>
-      <c r="E154" s="105">
+      <c r="E162" s="76">
         <v>2</v>
       </c>
-      <c r="F154" s="106" t="s">
+      <c r="F162" s="77" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="155" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C155" s="101">
+    <row r="163" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C163" s="72">
         <v>2</v>
       </c>
-      <c r="D155" s="102" t="s">
+      <c r="D163" s="73" t="s">
         <v>646</v>
       </c>
-      <c r="E155" s="102">
+      <c r="E163" s="73">
         <v>2</v>
       </c>
-      <c r="F155" s="103" t="s">
+      <c r="F163" s="74" t="s">
         <v>654</v>
       </c>
-      <c r="H155" t="s">
+      <c r="H163" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="156" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C156" s="104">
+    <row r="164" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C164" s="75">
         <v>2</v>
       </c>
-      <c r="D156" s="105" t="s">
+      <c r="D164" s="76" t="s">
         <v>647</v>
       </c>
-      <c r="E156" s="105">
+      <c r="E164" s="76">
         <v>2</v>
       </c>
-      <c r="F156" s="106" t="s">
+      <c r="F164" s="77" t="s">
         <v>654</v>
       </c>
-      <c r="H156" t="s">
+      <c r="H164" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="157" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C157" s="101">
+    <row r="165" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C165" s="72">
         <v>3</v>
       </c>
-      <c r="D157" s="102" t="s">
+      <c r="D165" s="73" t="s">
         <v>648</v>
       </c>
-      <c r="E157" s="102">
+      <c r="E165" s="73">
         <v>3</v>
       </c>
-      <c r="F157" s="103" t="s">
+      <c r="F165" s="74" t="s">
         <v>510</v>
       </c>
-      <c r="H157" t="s">
+      <c r="H165" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="158" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C158" s="107">
+    <row r="166" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C166" s="78">
         <v>3</v>
       </c>
-      <c r="D158" s="108" t="s">
+      <c r="D166" s="79" t="s">
         <v>649</v>
       </c>
-      <c r="E158" s="108">
+      <c r="E166" s="79">
         <v>3</v>
       </c>
-      <c r="F158" s="109" t="s">
+      <c r="F166" s="80" t="s">
         <v>510</v>
       </c>
-      <c r="H158" t="s">
+      <c r="H166" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="159" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C159" s="104">
+    <row r="167" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C167" s="75">
         <v>3</v>
       </c>
-      <c r="D159" s="105" t="s">
+      <c r="D167" s="76" t="s">
         <v>650</v>
       </c>
-      <c r="E159" s="105">
+      <c r="E167" s="76">
         <v>3</v>
       </c>
-      <c r="F159" s="106" t="s">
+      <c r="F167" s="77" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="160" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C160" s="101">
+    <row r="168" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C168" s="72">
         <v>3</v>
       </c>
-      <c r="D160" s="102" t="s">
+      <c r="D168" s="73" t="s">
         <v>648</v>
       </c>
-      <c r="E160" s="102">
+      <c r="E168" s="73">
         <v>3</v>
       </c>
-      <c r="F160" s="103" t="s">
+      <c r="F168" s="74" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="161" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C161" s="107">
+    <row r="169" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C169" s="78">
         <v>3</v>
       </c>
-      <c r="D161" s="108" t="s">
+      <c r="D169" s="79" t="s">
         <v>649</v>
       </c>
-      <c r="E161" s="108">
+      <c r="E169" s="79">
         <v>3</v>
       </c>
-      <c r="F161" s="109" t="s">
+      <c r="F169" s="80" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="162" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C162" s="104">
+    <row r="170" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C170" s="75">
         <v>3</v>
       </c>
-      <c r="D162" s="105" t="s">
+      <c r="D170" s="76" t="s">
         <v>650</v>
       </c>
-      <c r="E162" s="105">
+      <c r="E170" s="76">
         <v>3</v>
       </c>
-      <c r="F162" s="106" t="s">
+      <c r="F170" s="77" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="163" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C163" s="92" t="s">
+    <row r="171" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C171" s="63" t="s">
         <v>157</v>
       </c>
-      <c r="D163" s="93" t="s">
+      <c r="D171" s="64" t="s">
         <v>157</v>
       </c>
-      <c r="E163" s="93">
+      <c r="E171" s="64">
         <v>5</v>
       </c>
-      <c r="F163" s="94" t="s">
+      <c r="F171" s="65" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="164" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C164" s="95" t="s">
+    <row r="172" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C172" s="66" t="s">
         <v>157</v>
       </c>
-      <c r="D164" s="96" t="s">
+      <c r="D172" s="67" t="s">
         <v>157</v>
       </c>
-      <c r="E164" s="96">
+      <c r="E172" s="67">
         <v>5</v>
       </c>
-      <c r="F164" s="97" t="s">
+      <c r="F172" s="68" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="165" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C165" s="98" t="s">
+    <row r="173" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C173" s="69" t="s">
         <v>157</v>
       </c>
-      <c r="D165" s="99" t="s">
+      <c r="D173" s="70" t="s">
         <v>157</v>
       </c>
-      <c r="E165" s="99">
+      <c r="E173" s="70">
         <v>6</v>
       </c>
-      <c r="F165" s="100" t="s">
+      <c r="F173" s="71" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="168" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C168" t="s">
+    <row r="176" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C176" t="s">
         <v>642</v>
       </c>
-      <c r="E168" t="s">
+      <c r="E176" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="169" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C169" s="14" t="s">
+    <row r="177" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C177" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="D169" s="15" t="s">
+      <c r="D177" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="E169" s="15" t="s">
+      <c r="E177" s="15" t="s">
         <v>277</v>
       </c>
-      <c r="F169" s="16" t="s">
+      <c r="F177" s="16" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="170" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C170" s="101">
+    <row r="178" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C178" s="72">
         <v>2</v>
       </c>
-      <c r="D170" s="102" t="s">
+      <c r="D178" s="73" t="s">
         <v>646</v>
       </c>
-      <c r="E170" s="102">
+      <c r="E178" s="73">
         <v>2</v>
       </c>
-      <c r="F170" s="103" t="s">
+      <c r="F178" s="74" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="171" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C171" s="107">
+    <row r="179" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C179" s="78">
         <v>2</v>
       </c>
-      <c r="D171" s="108" t="s">
+      <c r="D179" s="79" t="s">
         <v>646</v>
       </c>
-      <c r="E171" s="108">
+      <c r="E179" s="79">
         <v>2</v>
       </c>
-      <c r="F171" s="109" t="s">
+      <c r="F179" s="80" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="172" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C172" s="104">
+    <row r="180" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C180" s="75">
         <v>2</v>
       </c>
-      <c r="D172" s="105" t="s">
+      <c r="D180" s="76" t="s">
         <v>646</v>
       </c>
-      <c r="E172" s="105">
+      <c r="E180" s="76">
         <v>2</v>
       </c>
-      <c r="F172" s="106" t="s">
+      <c r="F180" s="77" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="173" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C173" s="101">
+    <row r="181" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C181" s="72">
         <v>2</v>
       </c>
-      <c r="D173" s="102" t="s">
+      <c r="D181" s="73" t="s">
         <v>647</v>
       </c>
-      <c r="E173" s="102">
+      <c r="E181" s="73">
         <v>2</v>
       </c>
-      <c r="F173" s="103" t="s">
+      <c r="F181" s="74" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="174" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C174" s="107">
+    <row r="182" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C182" s="78">
         <v>2</v>
       </c>
-      <c r="D174" s="108" t="s">
+      <c r="D182" s="79" t="s">
         <v>647</v>
       </c>
-      <c r="E174" s="108">
+      <c r="E182" s="79">
         <v>2</v>
       </c>
-      <c r="F174" s="109" t="s">
+      <c r="F182" s="80" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="175" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C175" s="104">
+    <row r="183" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C183" s="75">
         <v>2</v>
       </c>
-      <c r="D175" s="105" t="s">
+      <c r="D183" s="76" t="s">
         <v>647</v>
       </c>
-      <c r="E175" s="105">
+      <c r="E183" s="76">
         <v>2</v>
       </c>
-      <c r="F175" s="106" t="s">
+      <c r="F183" s="77" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="176" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C176" s="101">
+    <row r="184" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C184" s="72">
         <v>3</v>
       </c>
-      <c r="D176" s="102" t="s">
+      <c r="D184" s="73" t="s">
         <v>648</v>
       </c>
-      <c r="E176" s="102">
+      <c r="E184" s="73">
         <v>3</v>
       </c>
-      <c r="F176" s="103" t="s">
+      <c r="F184" s="74" t="s">
         <v>510</v>
       </c>
-      <c r="H176" t="s">
+      <c r="H184" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="177" spans="3:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C177" s="104">
+    <row r="185" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C185" s="75">
         <v>3</v>
       </c>
-      <c r="D177" s="105" t="s">
+      <c r="D185" s="76" t="s">
         <v>648</v>
       </c>
-      <c r="E177" s="105">
+      <c r="E185" s="76">
         <v>3</v>
       </c>
-      <c r="F177" s="106" t="s">
+      <c r="F185" s="77" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="178" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C178" s="101">
+    <row r="186" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C186" s="72">
         <v>3</v>
       </c>
-      <c r="D178" s="102" t="s">
+      <c r="D186" s="73" t="s">
         <v>649</v>
       </c>
-      <c r="E178" s="102">
+      <c r="E186" s="73">
         <v>3</v>
       </c>
-      <c r="F178" s="103" t="s">
+      <c r="F186" s="74" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="179" spans="3:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C179" s="104">
+    <row r="187" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C187" s="75">
         <v>3</v>
       </c>
-      <c r="D179" s="105" t="s">
+      <c r="D187" s="76" t="s">
         <v>649</v>
       </c>
-      <c r="E179" s="105">
+      <c r="E187" s="76">
         <v>3</v>
       </c>
-      <c r="F179" s="106" t="s">
+      <c r="F187" s="77" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="180" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C180" s="107">
+    <row r="188" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C188" s="78">
         <v>3</v>
       </c>
-      <c r="D180" s="108" t="s">
+      <c r="D188" s="79" t="s">
         <v>650</v>
       </c>
-      <c r="E180" s="108">
+      <c r="E188" s="79">
         <v>3</v>
       </c>
-      <c r="F180" s="109" t="s">
+      <c r="F188" s="80" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="181" spans="3:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C181" s="104">
+    <row r="189" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C189" s="75">
         <v>3</v>
       </c>
-      <c r="D181" s="105" t="s">
+      <c r="D189" s="76" t="s">
         <v>650</v>
       </c>
-      <c r="E181" s="105">
+      <c r="E189" s="76">
         <v>3</v>
       </c>
-      <c r="F181" s="106" t="s">
+      <c r="F189" s="77" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="182" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C182" s="110">
+    <row r="190" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C190" s="81">
         <v>1</v>
       </c>
-      <c r="D182" s="111" t="s">
+      <c r="D190" s="82" t="s">
         <v>611</v>
       </c>
-      <c r="E182" s="111" t="s">
+      <c r="E190" s="82" t="s">
         <v>157</v>
       </c>
-      <c r="F182" s="112" t="s">
+      <c r="F190" s="83" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="183" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C183" s="113">
+    <row r="191" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C191" s="84">
         <v>1</v>
       </c>
-      <c r="D183" s="114" t="s">
+      <c r="D191" s="85" t="s">
         <v>645</v>
       </c>
-      <c r="E183" s="114" t="s">
+      <c r="E191" s="85" t="s">
         <v>157</v>
       </c>
-      <c r="F183" s="115" t="s">
+      <c r="F191" s="86" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="184" spans="3:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C184" s="119">
+    <row r="192" spans="3:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C192" s="90">
         <v>4</v>
       </c>
-      <c r="D184" s="120" t="s">
+      <c r="D192" s="91" t="s">
         <v>651</v>
       </c>
-      <c r="E184" s="120" t="s">
+      <c r="E192" s="91" t="s">
         <v>157</v>
       </c>
-      <c r="F184" s="121" t="s">
+      <c r="F192" s="92" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="185" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C185" s="92" t="s">
+    <row r="193" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C193" s="63" t="s">
         <v>157</v>
       </c>
-      <c r="D185" s="93" t="s">
+      <c r="D193" s="64" t="s">
         <v>157</v>
       </c>
-      <c r="E185" s="93">
+      <c r="E193" s="64">
         <v>5</v>
       </c>
-      <c r="F185" s="94" t="s">
+      <c r="F193" s="65" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="186" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C186" s="95" t="s">
+    <row r="194" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C194" s="66" t="s">
         <v>157</v>
       </c>
-      <c r="D186" s="96" t="s">
+      <c r="D194" s="67" t="s">
         <v>157</v>
       </c>
-      <c r="E186" s="96">
+      <c r="E194" s="67">
         <v>5</v>
       </c>
-      <c r="F186" s="97" t="s">
+      <c r="F194" s="68" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="187" spans="3:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C187" s="98" t="s">
+    <row r="195" spans="3:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C195" s="69" t="s">
         <v>157</v>
       </c>
-      <c r="D187" s="99" t="s">
+      <c r="D195" s="70" t="s">
         <v>157</v>
       </c>
-      <c r="E187" s="99">
+      <c r="E195" s="70">
         <v>6</v>
       </c>
-      <c r="F187" s="100" t="s">
+      <c r="F195" s="71" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="192" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="E192" t="s">
+    <row r="200" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="E200" t="s">
         <v>659</v>
       </c>
-      <c r="F192" t="s">
+      <c r="F200" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="193" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="E193" t="s">
+    <row r="201" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="E201" t="s">
         <v>661</v>
       </c>
-      <c r="F193" t="s">
+      <c r="F201" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="194" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="E194" t="s">
+    <row r="202" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="E202" t="s">
         <v>665</v>
       </c>
-      <c r="F194" t="s">
+      <c r="F202" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="195" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="E195" t="s">
+    <row r="203" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="E203" t="s">
         <v>668</v>
       </c>
-      <c r="F195" t="s">
+      <c r="F203" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="198" spans="3:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C198" t="s">
+    <row r="206" spans="3:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C206" t="s">
         <v>673</v>
       </c>
-      <c r="G198" t="s">
+      <c r="G206" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="199" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C199" s="2"/>
-      <c r="D199" s="3"/>
-      <c r="E199" s="4"/>
-      <c r="G199" s="2"/>
-      <c r="H199" s="3"/>
-      <c r="I199" s="4"/>
-    </row>
-    <row r="200" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C200" s="5"/>
-      <c r="D200" s="89"/>
-      <c r="E200" s="6"/>
-      <c r="G200" s="5"/>
-      <c r="H200" s="89"/>
-      <c r="I200" s="6"/>
-    </row>
-    <row r="201" spans="3:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C201" s="5"/>
-      <c r="D201" s="89"/>
-      <c r="E201" s="6"/>
-      <c r="G201" s="7"/>
-      <c r="H201" s="8"/>
-      <c r="I201" s="9"/>
-    </row>
-    <row r="202" spans="3:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C202" s="5"/>
-      <c r="D202" s="89"/>
-      <c r="E202" s="6"/>
-    </row>
-    <row r="203" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C203" s="5"/>
-      <c r="D203" s="89"/>
-      <c r="E203" s="6"/>
-      <c r="G203" s="2"/>
-      <c r="H203" s="3"/>
-      <c r="I203" s="4"/>
-    </row>
-    <row r="204" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C204" s="5"/>
-      <c r="D204" s="89"/>
-      <c r="E204" s="6"/>
-      <c r="G204" s="5"/>
-      <c r="H204" s="89"/>
-      <c r="I204" s="6"/>
-    </row>
-    <row r="205" spans="3:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C205" s="5"/>
-      <c r="D205" s="89"/>
-      <c r="E205" s="6"/>
-      <c r="G205" s="7"/>
-      <c r="H205" s="8"/>
-      <c r="I205" s="9"/>
-    </row>
-    <row r="206" spans="3:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C206" s="5"/>
-      <c r="D206" s="89"/>
-      <c r="E206" s="6"/>
-    </row>
-    <row r="207" spans="3:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C207" s="7"/>
-      <c r="D207" s="8"/>
-      <c r="E207" s="9"/>
+    <row r="207" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C207" s="2"/>
+      <c r="D207" s="3"/>
+      <c r="E207" s="4"/>
       <c r="G207" s="2"/>
       <c r="H207" s="3"/>
       <c r="I207" s="4"/>
     </row>
     <row r="208" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C208" s="5"/>
+      <c r="E208" s="6"/>
       <c r="G208" s="5"/>
-      <c r="H208" s="89"/>
       <c r="I208" s="6"/>
     </row>
     <row r="209" spans="3:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C209" s="5"/>
+      <c r="E209" s="6"/>
       <c r="G209" s="7"/>
       <c r="H209" s="8"/>
       <c r="I209" s="9"/>
     </row>
-    <row r="213" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C213" t="s">
+    <row r="210" spans="3:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C210" s="5"/>
+      <c r="E210" s="6"/>
+    </row>
+    <row r="211" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C211" s="5"/>
+      <c r="E211" s="6"/>
+      <c r="G211" s="2"/>
+      <c r="H211" s="3"/>
+      <c r="I211" s="4"/>
+    </row>
+    <row r="212" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C212" s="5"/>
+      <c r="E212" s="6"/>
+      <c r="G212" s="5"/>
+      <c r="I212" s="6"/>
+    </row>
+    <row r="213" spans="3:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C213" s="5"/>
+      <c r="E213" s="6"/>
+      <c r="G213" s="7"/>
+      <c r="H213" s="8"/>
+      <c r="I213" s="9"/>
+    </row>
+    <row r="214" spans="3:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C214" s="5"/>
+      <c r="E214" s="6"/>
+    </row>
+    <row r="215" spans="3:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C215" s="7"/>
+      <c r="D215" s="8"/>
+      <c r="E215" s="9"/>
+      <c r="G215" s="2"/>
+      <c r="H215" s="3"/>
+      <c r="I215" s="4"/>
+    </row>
+    <row r="216" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="G216" s="5"/>
+      <c r="I216" s="6"/>
+    </row>
+    <row r="217" spans="3:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G217" s="7"/>
+      <c r="H217" s="8"/>
+      <c r="I217" s="9"/>
+    </row>
+    <row r="221" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C221" t="s">
         <v>16</v>
       </c>
-      <c r="G213" t="s">
+      <c r="G221" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="214" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C214" t="s">
+    <row r="222" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C222" t="s">
         <v>17</v>
       </c>
-      <c r="G214" t="s">
+      <c r="G222" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="215" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C215" t="s">
-        <v>675</v>
-      </c>
-      <c r="G215" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="216" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C216" t="s">
-        <v>24</v>
-      </c>
-      <c r="G216" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="217" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C217" t="s">
-        <v>22</v>
-      </c>
-      <c r="G217" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="218" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C218" t="s">
-        <v>324</v>
-      </c>
-      <c r="G218" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="223" spans="3:9" x14ac:dyDescent="0.2">
       <c r="C223" t="s">
-        <v>18</v>
+        <v>675</v>
       </c>
       <c r="G223" t="s">
-        <v>19</v>
+        <v>675</v>
       </c>
     </row>
     <row r="224" spans="3:9" x14ac:dyDescent="0.2">
       <c r="C224" t="s">
+        <v>24</v>
+      </c>
+      <c r="G224" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="225" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C225" t="s">
+        <v>22</v>
+      </c>
+      <c r="G225" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="226" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C226" t="s">
+        <v>324</v>
+      </c>
+      <c r="G226" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="231" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C231" t="s">
+        <v>18</v>
+      </c>
+      <c r="G231" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="232" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C232" t="s">
         <v>277</v>
       </c>
-      <c r="D224" t="s">
+      <c r="D232" t="s">
         <v>80</v>
       </c>
-      <c r="G224" t="s">
+      <c r="G232" t="s">
         <v>277</v>
       </c>
-      <c r="H224" t="s">
+      <c r="H232" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="227" spans="3:10" x14ac:dyDescent="0.2">
-      <c r="E227" t="s">
+    <row r="235" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="E235" t="s">
         <v>676</v>
-      </c>
-    </row>
-    <row r="230" spans="3:10" x14ac:dyDescent="0.2">
-      <c r="C230" t="s">
-        <v>274</v>
-      </c>
-      <c r="G230" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="231" spans="3:10" x14ac:dyDescent="0.2">
-      <c r="D231" t="s">
-        <v>682</v>
-      </c>
-      <c r="H231" t="s">
-        <v>683</v>
-      </c>
-      <c r="J231" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="232" spans="3:10" x14ac:dyDescent="0.2">
-      <c r="J232" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="233" spans="3:10" x14ac:dyDescent="0.2">
-      <c r="C233" t="s">
-        <v>677</v>
-      </c>
-      <c r="G233" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="234" spans="3:10" x14ac:dyDescent="0.2">
-      <c r="D234" t="s">
-        <v>18</v>
-      </c>
-      <c r="E234" t="s">
-        <v>680</v>
-      </c>
-      <c r="H234" t="s">
-        <v>18</v>
-      </c>
-      <c r="J234" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="235" spans="3:10" x14ac:dyDescent="0.2">
-      <c r="J235" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="236" spans="3:10" x14ac:dyDescent="0.2">
-      <c r="C236" t="s">
-        <v>678</v>
-      </c>
-      <c r="G236" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="237" spans="3:10" x14ac:dyDescent="0.2">
-      <c r="D237" t="s">
-        <v>19</v>
-      </c>
-      <c r="E237" t="s">
-        <v>681</v>
-      </c>
-      <c r="H237" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="238" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C238" t="s">
+        <v>274</v>
+      </c>
+      <c r="G238" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="239" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="D239" t="s">
+        <v>682</v>
+      </c>
+      <c r="H239" t="s">
+        <v>683</v>
+      </c>
+      <c r="J239" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="240" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="J240" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="241" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C241" t="s">
+        <v>677</v>
+      </c>
+      <c r="G241" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="242" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="D242" t="s">
+        <v>18</v>
+      </c>
+      <c r="E242" t="s">
+        <v>680</v>
+      </c>
+      <c r="H242" t="s">
+        <v>18</v>
+      </c>
+      <c r="J242" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="243" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="J243" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="244" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C244" t="s">
+        <v>678</v>
+      </c>
+      <c r="G244" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="245" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="D245" t="s">
+        <v>19</v>
+      </c>
+      <c r="E245" t="s">
+        <v>681</v>
+      </c>
+      <c r="H245" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="246" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C246" t="s">
         <v>679</v>
       </c>
-      <c r="G238" t="s">
+      <c r="G246" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="239" spans="3:10" x14ac:dyDescent="0.2">
-      <c r="D239" s="122" t="s">
+    <row r="247" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="D247" s="93" t="s">
         <v>676</v>
       </c>
-      <c r="H239" s="122" t="s">
+      <c r="H247" s="93" t="s">
         <v>676</v>
+      </c>
+    </row>
+    <row r="249" spans="3:11" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="250" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="E250" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="F250" s="3"/>
+      <c r="G250" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="H250" s="3"/>
+      <c r="I250" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="K250" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="251" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="E251" s="5" t="s">
+        <v>689</v>
+      </c>
+      <c r="G251" t="s">
+        <v>693</v>
+      </c>
+      <c r="I251" s="6" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="252" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="E252" s="5" t="s">
+        <v>690</v>
+      </c>
+      <c r="G252" t="s">
+        <v>694</v>
+      </c>
+      <c r="I252" s="6" t="s">
+        <v>697</v>
+      </c>
+      <c r="K252" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="253" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="E253" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="I253" s="6" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="254" spans="3:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E254" s="7" t="s">
+        <v>699</v>
+      </c>
+      <c r="F254" s="8"/>
+      <c r="G254" s="8"/>
+      <c r="H254" s="8"/>
+      <c r="I254" s="9"/>
+    </row>
+    <row r="257" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C257" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="258" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C258" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="262" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C262" t="s">
+        <v>22</v>
+      </c>
+      <c r="G262" t="s">
+        <v>704</v>
+      </c>
+      <c r="I262" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="264" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C264">
+        <v>1</v>
+      </c>
+      <c r="D264">
+        <v>1</v>
+      </c>
+      <c r="E264">
+        <v>1</v>
+      </c>
+      <c r="G264">
+        <v>1</v>
+      </c>
+      <c r="I264">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C265">
+        <v>2</v>
+      </c>
+      <c r="D265">
+        <v>1</v>
+      </c>
+      <c r="E265">
+        <v>1</v>
+      </c>
+      <c r="G265">
+        <v>2</v>
+      </c>
+      <c r="I265">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="266" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C266">
+        <v>3</v>
+      </c>
+      <c r="E266">
+        <v>1</v>
+      </c>
+      <c r="G266">
+        <v>3</v>
+      </c>
+      <c r="I266">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="267" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C267">
+        <v>4</v>
+      </c>
+      <c r="D267">
+        <v>2</v>
+      </c>
+      <c r="G267">
+        <v>4</v>
+      </c>
+      <c r="I267">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="268" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C268">
+        <v>5</v>
+      </c>
+      <c r="D268">
+        <v>2</v>
+      </c>
+      <c r="E268">
+        <v>3</v>
+      </c>
+      <c r="G268">
+        <v>5</v>
+      </c>
+      <c r="I268">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="272" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="E272" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="273" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C273" t="s">
+        <v>17</v>
+      </c>
+      <c r="D273">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="274" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C274" t="s">
+        <v>706</v>
+      </c>
+      <c r="D274">
+        <v>50000</v>
+      </c>
+      <c r="E274">
+        <v>47521</v>
+      </c>
+      <c r="F274">
+        <f>D274-E274</f>
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="277" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="D277">
+        <v>152479</v>
+      </c>
+    </row>
+    <row r="280" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="D280" t="s">
+        <v>708</v>
+      </c>
+      <c r="E280">
+        <f>D273</f>
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="281" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="D281" t="s">
+        <v>709</v>
+      </c>
+      <c r="E281">
+        <f>F274</f>
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="282" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="E282">
+        <f>SUM(E280:E281)</f>
+        <v>152479</v>
+      </c>
+    </row>
+    <row r="287" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="D287" t="s">
+        <v>188</v>
+      </c>
+      <c r="E287" t="s">
+        <v>719</v>
+      </c>
+      <c r="G287" t="s">
+        <v>188</v>
+      </c>
+      <c r="H287" t="s">
+        <v>311</v>
+      </c>
+      <c r="I287" t="s">
+        <v>710</v>
+      </c>
+      <c r="J287">
+        <v>150000</v>
+      </c>
+      <c r="K287">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="288" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="D288" t="s">
+        <v>710</v>
+      </c>
+      <c r="E288" t="s">
+        <v>720</v>
+      </c>
+      <c r="G288" t="s">
+        <v>711</v>
+      </c>
+      <c r="H288" t="s">
+        <v>311</v>
+      </c>
+      <c r="I288" t="s">
+        <v>719</v>
+      </c>
+      <c r="J288">
+        <v>200000</v>
+      </c>
+      <c r="K288">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="289" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D289" t="s">
+        <v>711</v>
+      </c>
+      <c r="J289">
+        <f>J288*K288</f>
+        <v>10000000000</v>
+      </c>
+    </row>
+    <row r="290" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D290" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="291" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D291" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="292" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D292" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="293" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D293" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="294" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D294" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="295" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D295" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="296" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D296" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="298" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D298" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="299" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D299" t="s">
+        <v>722</v>
       </c>
     </row>
   </sheetData>
@@ -15765,6 +18415,7 @@
     <mergeCell ref="J24:M27"/>
     <mergeCell ref="J39:M42"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/batch_notes/28/batch_28.xlsx
+++ b/batch_notes/28/batch_28.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10819"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/shira_2/__work__/acciojob/modules/sql/postgresql/batch_notes/28/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33391F5C-9BF9-4040-9E83-25B3D02CD98B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C6F2891-C59B-CB4E-B1F4-9273FA0399E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-2480" windowWidth="38400" windowHeight="21600" activeTab="9" xr2:uid="{C88571CB-2605-694D-B9DF-E4D6E422F2C7}"/>
+    <workbookView xWindow="-38400" yWindow="-2480" windowWidth="38400" windowHeight="21600" activeTab="10" xr2:uid="{C88571CB-2605-694D-B9DF-E4D6E422F2C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Intro to SQL" sheetId="1" r:id="rId1"/>
@@ -23,12 +23,13 @@
     <sheet name="Aggregate Functions &amp; Group By" sheetId="8" r:id="rId8"/>
     <sheet name="Join Part 1 &amp; 2" sheetId="9" r:id="rId9"/>
     <sheet name="Self Join" sheetId="10" r:id="rId10"/>
+    <sheet name="Subquery" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId11"/>
-    <pivotCache cacheId="1" r:id="rId12"/>
-    <pivotCache cacheId="2" r:id="rId13"/>
+    <pivotCache cacheId="0" r:id="rId12"/>
+    <pivotCache cacheId="1" r:id="rId13"/>
+    <pivotCache cacheId="2" r:id="rId14"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -75,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="773">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="785">
   <si>
     <t>Warehouse</t>
   </si>
@@ -2424,6 +2425,42 @@
   </si>
   <si>
     <t>Food Taste</t>
+  </si>
+  <si>
+    <t>Complete Value</t>
+  </si>
+  <si>
+    <t>part of the string</t>
+  </si>
+  <si>
+    <t>Outer</t>
+  </si>
+  <si>
+    <t>Execute Inner</t>
+  </si>
+  <si>
+    <t>Output of inner will be used by Outer Query</t>
+  </si>
+  <si>
+    <t>Quter Query will be executed and we get the result</t>
+  </si>
+  <si>
+    <t>OutPut</t>
+  </si>
+  <si>
+    <t>Multi Row</t>
+  </si>
+  <si>
+    <t>Derived Table</t>
+  </si>
+  <si>
+    <t>If you have one ticket for concert how many people can go</t>
+  </si>
+  <si>
+    <t>If we have group ticket where I can have 5 people</t>
+  </si>
+  <si>
+    <t>IN | NOT IN</t>
   </si>
 </sst>
 </file>
@@ -2765,7 +2802,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -2862,6 +2899,10 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2937,10 +2978,15 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6727,6 +6773,579 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>368300</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>15373</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4340FC3D-70B7-814D-D2B5-2E6FDE2B8C7D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="825500" y="203200"/>
+          <a:ext cx="7772400" cy="4079373"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>787400</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>387350</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Frame 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6030AA0-01A3-3635-A3B3-98A0E0851DF4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="787400" y="215900"/>
+          <a:ext cx="7829550" cy="4051300"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 2312"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Frame 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7779D85D-75B3-8E46-BE95-5CC7A405D78D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1244600" y="2673350"/>
+          <a:ext cx="7213600" cy="1454150"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 4432"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>660400</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Frame 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E77E77FD-619A-594A-AEFA-457E8F5C7B53}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="850900" y="4489450"/>
+          <a:ext cx="5588000" cy="2089150"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 2312"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>565150</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>482600</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Frame 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAE593D4-3674-7B42-8586-B9F50C2B299A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1390650" y="4972050"/>
+          <a:ext cx="4870450" cy="1492250"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 4432"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>617620</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>112760</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>504560</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>108480</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="7" name="Ink 6">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EBAFF0E-BA5B-4EAF-5C13-2C2B3E925D5D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="6396120" y="4583160"/>
+            <a:ext cx="712440" cy="402120"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="7" name="Ink 6">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EBAFF0E-BA5B-4EAF-5C13-2C2B3E925D5D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6391800" y="4578840"/>
+              <a:ext cx="721080" cy="410760"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>769920</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>160320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>399460</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>141640</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="8" name="Ink 7">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D085D25-E51C-3274-5C47-3437FEA3AD30}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="5722920" y="5037120"/>
+            <a:ext cx="455040" cy="387720"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="8" name="Ink 7">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D085D25-E51C-3274-5C47-3437FEA3AD30}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5718600" y="5032800"/>
+              <a:ext cx="463680" cy="396360"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>448440</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>60840</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>713360</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>129120</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="21" name="Ink 20">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E1F5FC4-8EB9-4AE1-59E7-BB336ED1C60E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="5401440" y="5547240"/>
+            <a:ext cx="1915920" cy="677880"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="21" name="Ink 20">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E1F5FC4-8EB9-4AE1-59E7-BB336ED1C60E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5397120" y="5542920"/>
+              <a:ext cx="1924560" cy="686520"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>52580</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>152320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>699860</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>92600</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="22" name="Ink 21">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{761913C4-06C0-74FC-206B-41DD2344C1FD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="7456680" y="13588920"/>
+            <a:ext cx="647280" cy="346680"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="22" name="Ink 21">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{761913C4-06C0-74FC-206B-41DD2344C1FD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7452360" y="13584600"/>
+              <a:ext cx="655920" cy="355320"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/ink/ink1.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
@@ -7533,6 +8152,124 @@
     </inkml:brush>
   </inkml:definitions>
   <inkml:trace contextRef="#ctx0" brushRef="#br0">4730 484,'-41'1,"1"5,13 16,-18 14,-4 3,5-4,14-8,17-17,1 7,3-5,1-1,-20 26,0-7,-11 16,14-15,5 3,7-5,-7 5,1 2,-23 22,8 15,-8 4,20-10,1 2,-11 21,2 2,-1 2,13-35,-1-4,-7 10,1-4,4 15,0-36,11-10,-1-6,5-10,-5 14,7-9,-1-2,5-3,-3-2,3 10,-2-7,4 7,8 21,0 30,3-5,-7-1,-2-38,0-2,3-4,5 20,-2-24,0 23,-7-31,2 14,-1-13,14 51,9 20,-15-33,1 0,18 43,-16-46,1-17,-8-15,-1-8,3 7,5-3,0 4,-1-5,-2-7,14 45,-12-13,20 50,-26-47,5-3,-9-23,-4 15,5 6,-4 9,4-13,-5-11,-17 69,14-2,2 7,-8-9,1 1,6 17,4-14,0-35,15-12,-6-34,11 13,-12-16,1 4,10-4,0 12,8 15,-2 1,-11 13,0-19,-9-5,-2-6,2-4,2 5,2 7,-2-8,4 4,-1-12,6-1,-3-2,4-6,-3 3,-3-2,17 2,-18 0,14 2,-14 3,6 3,-7 2,3 1,2 2,14 7,-6-7,4 3,-23-11,-5 19,5 52,5 7,2-4,1-2,3-7,-2 7,-19-75,-1-2,-23-7,16 6,-19-4,6 13,-24 0,-33 13,7-5,-6 0,7 1,2-1,1 1,4-2,-17 5,61-13,5-2,5 2,0-1,-23 7,15-5,-24 5,18-9,-12 0,8-4,4 0,3 0,13 0,-26 0,-12 8,0-2,2 6,24-5,11-4,1-1,-17-2,15 0,-12 0,16 0,-4 0,-4-5,-34-7,23 4,-30-10,4 1,-9-1,-30-4,-6-1,9 0,-1 0,19 8,-3 2,13 1,-13-3,8-1,2 1,-9 2,21 6,1 0,-22 0,15-5,39 2,-50-36,-4 5,18 5,2 0,-12-1,24 3,27 19,-8-9,-18-17,-11 5,-16-22,3 22,9-3,2 0,29 24,-8-21,19 23,-41-53,17 33,-5-14,-2-2,-16-4,20 11,1 0,-7 0,10 3,15 14,-10-29,-4-5,-15-13,-6-7,19 22,1 1,-16-17,0-1,7 10,3 4,10 11,0 1,-3 0,2 1,-13-29,27 43,8 3,8 18,0 0,1-18,0-32,0-14,9 3,2-2,-3 23,0-1,4-25,2 0,4 19,-1 2,-3 1,2-1,11-10,3 2,-7 17,2 0,9-14,2-2,2 1,0 3,-7 16,-1 0,2-6,0 0,18-26,-19 31,2-1,0 3,0-1,5-9,1 2,25-23,-4-5,-16 30,-5 1,-11 11,13-7,0 1,19-5,-1 4,-16 14,4-2,19-17,0-1,-12 16,1 1,27-20,-2 4,4 9,-26 18,0 1,11-6,6 1,-14-5,3-4,-7 6,0 0,7-5,-1 1,-8 5,-1 4,38 0,-3 2,12 12,-47 7,3 3,34 6,8 1,0-6,5 1,-3 6,5 3,-9-3,-10-5,-7-1,4 4,-15 2,-35-2,-4 3,-7 4,6 5,-7-5,2 2,-9-8,3 1,-59 22,-4-3,-8 2,-13 5,-10 4,10-7,-10 4,-1 2,4-1,-9 10,5 2,-3-2,15-10,-4 0,3 0,4-1,3 4,4-1,2-1,-22 14,3-3,19-14,1 0,-6 10,4-2,-3 4,33-15,8-14,-21 41,17-21,-7 16,31-28,4-21,62 1,-12-11,8-6,8-4,9-4,3-7,-6-6,4-6,1-3,-3-1,-3 4,-1-2,-1-1,-2-3,1-6,0-5,-4 1,-5 4,-3 6,-5 2,-7 3,-3-6,-7 6,5 3,-40 27,-58 25,-53 29,-2 3,34-15,-1 2,-4 2,-5 4,15-7,-6 3,-2 3,-3 0,0 2,2 0,2 1,-10 5,1 2,1 0,2 1,2 0,4 1,-1 2,4 0,2 0,3 2,3 1,-12 13,3 4,5-3,10-7,-4 6,13-6,13-2,16-15,23-39,5-2,60-33,32-24,-30 19,4-3,12-11,-23 11,9-7,7-5,4-4,3-2,0-1,-3 1,-4 3,-6 3,5-4,-5 2,-3 1,-1 0,2-1,3-3,5-3,5-4,4-2,-2 0,-4 2,-9 3,-10 7,5-14,-13 6,-14 13,-8 10,-90 101,13-9,-9 12,-6 7,4-10,-5 5,-3 4,-3 3,-1 4,17-18,-2 3,-1 3,-1 2,0 0,1 0,2-2,2-3,-6 9,3-2,1-1,1-1,1-1,1 1,-10 10,-1 3,3-2,6-6,13-12,-1 12,24-21,29-36,23-49,13-25,-1 10,5-4,4-5,3-8,3-7,2-2,1 0,2 1,1 0,2-1,3-4,-12 12,3-5,2-2,-2 2,-3 3,-6 8,8-9,-6 7,0 0,20-21,1-1,-39 46,-62 74,-13 22,-12 20,-1 3,15-20,0 2,-1 1,-1 4,0-1,-3 5,0 2,2-4,3-6,-2 8,3-6,6-7,0 6,15-29,14-40,39-75,-11 32,4-5,4-7,4-5,-3 3,0 0,-3 4,3-3,-11 26,-44 105,-3-15,-5 12,-5 5,-2 4,-4 5,-2 5,-1 1,3-5,-1 5,0 1,0-3,2-6,0-5,2-5,1-3,2-2,-11 21,3-3,27-44,41-67,13-24,2-15,4-13,-6 15,6-8,1-4,-3 3,-5 3,-1-1,-1 1,-1 2,7-13,-2 3,-3 7,2-9,-14 34,-27 51,-21 48,-21 37,-2 0,6-11,-1 0,-6 7,2-5,-6 9,-3 2,3-4,6-12,4-7,5-8,-1-2,-11 16,-1-1,24-43,28-47,28-45,9-18,-8 1,1-5,2 9,4-4,-7 7,-3-8,-14 34,-33 112,-17 48,12-47,-2 2,-2 8,1-4,-1 10,-1 2,1-2,4-9,0 7,4-8,2-6,-3 12,13-34,43-93,-10-4,2-12,2-11,3-11,-1 8,5 2,-3 6,-5-11,-9 32,-15 74,-17 52,-7 17,6-24,1 0,-6 22,5-11,10-34,19-70,12-33,7-16,-5 10,2-4,0 2,11-23,-3 4,-2 8,-8 16,-21 40,-24 79,-12 17,-12 11,2-13,62-123,15-30,-15 21,2-2,4-1,4-4,-4 10,16-11,-50 110,-11 33,-1 10,-3 9,0-6,-2 6,0-8,-1-3,0-15,-4-11,27-122,9-39,-3 11,1-1,3-7,0 8,3 5,-11 62,-6 24,26 22,16-5,4 2,18 17,-16-18,-6-5,-26-12,-10-26,-4-9,8-26,-7 22,2-3,-6 31,1 3</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink36.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-29T14:41:22.085"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.025" units="cm"/>
+      <inkml:brushProperty name="height" value="0.025" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1979 8 24575,'-2'-5'0,"-4"3"0,-11 7 0,1-2 0,-16 8 0,-5-4 0,-18 7 0,-24 5 0,11 1 0,-16 6 0,48-9 0,-2-1 0,28-9 0,-3 4 0,-23 3 0,1 2 0,-45 12 0,33-8 0,-21 10 0,17-5 0,10-2 0,6-5 0,16-8 0,12-10 0,0 0 0,-2 0 0,-38 23 0,-16 10 0,-11 8 0,11-5 0,-4 3 0,-3 2 0,4-5 0,-3 2 0,0 0 0,3-2 0,-8 7 0,4-2 0,5-4 0,-7 1 0,11-7 0,7-4 0,54-30 0,5-5 0,4-9 0,4-12 0,22-23 0,-6 4 0,11 1 0,-13 8 0,-4 15 0,-7 0 0,-5 6 0,-8 6 0,5-6 0,0 0 0,4-1 0,2 1 0,3-2 0,-4 5 0,2-2 0,-10 14 0,-5 2 0,-1 5 0,-3 3 0,4-3 0,-32 59 0,5-11 0,-17 34 0,10-20 0,9-20 0,5 3 0,-5-9 0,15-15 0,-2-6 0,10-12 0,0-3 0,-1 22 0,1-16 0,-1 16 0,10-24 0,14 0 0,24-5 0,28 2 0,-12-1 0,4 1 0,-10 5 0,0 1 0,3-1 0,-2 0 0,29 14 0,-49-8 0,3-2 0,-24 0 0,-4 5 0,5 4 0,-6-2 0,-3-6 0,-5-7 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink37.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-29T14:41:28.607"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.025" units="cm"/>
+      <inkml:brushProperty name="height" value="0.025" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1264 0 24575,'-21'9'0,"-47"41"0,9-4 0,-7 7 0,16-11 0,-3 2 0,-1 1-735,-12 5 0,-4 2 0,2 0 735,2 0 0,1 1 0,1-1 0,6-2 0,1 0 0,2-2 0,-14 10 0,7-3 353,16-6 1,11-9-354,17-23 364,8-8-364,6-18 0,-1-7 0,2-18 1134,-4-25-1134,3-6 0,-2-7 0,3 25 0,1 6 0,2 26 0,0 1 0,0 15 0,0 12 0,-10 54 0,-5 11 0,2 11 0,2-32 0,11-41 0,4-5 0,3 1 0,12 5 0,14 6 0,19-5 0,19 11 0,10-12 0,-27-3 0,-11-10 0,-33-5 0,-6 1 0,-2 3 0,-2-1 0,0 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink38.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-29T14:41:30.257"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.025" units="cm"/>
+      <inkml:brushProperty name="height" value="0.025" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 177 24575,'4'13'0,"4"-4"0,20 2 0,-6-8 0,10-1 0,-7-6 0,-9 1 0,6-6 0,-13 3 0,13-18 0,-9-3 0,6 0 0,-11 5 0,-8 20 0,-2 0 0,-5 2 0,-9-2 0,-11-1 0,2 0 0,0-1 0,16 3 0,5 1 0,-3 3 0,-8 8 0,4-4 0,-11 14 0,15-16 0,0 12 0,13-6 0,27 30 0,0-12 0,48 24 0,-16-34 0,-4-1 0,-10-15 0,-41-1 0,6-2 0,-12 2 0,6-9 0,-4 5 0,1-5 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="550">623 1 24575,'-15'30'0,"-14"17"0,-4 10 0,2 8 0,-1 1 0,-5 1 0,1 0 0,12-5 0,7-8 0,7-21 0,5-6 0,0-21 0,-14-9 0,6-9 0,-5 7 0,12-3 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1052">373 199 22356,'7'-4'0,"12"1"1077,2 4-1077,24 9 0,-11 10 374,36 40-374,-38-24 0,15 14 0,-39-39 0,-3-9 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1900">738 271 24575,'28'-5'0,"20"-4"0,3-2 0,1-2 0,-25 0 0,-10-6 0,-5-1 0,14-38 0,-12 19 0,3-8 0,-19 30 0,-5 15 0,-5 2 0,2 2 0,1-1 0,-3 5 0,6-5 0,-4 4 0,5 4 0,-9 9 0,0 13 0,-1-3 0,8 5 0,16-10 0,18-2 0,4-5 0,5-6 0,-1-6 0,-14-4 0,13-8 0,-17-4 0,5 1 0,-12 2 0,-12 7 0,3 2 0,-7 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2900">521 678 24575,'20'4'0,"0"13"0,1 33 0,-14 15 0,-6 8 0,-5-10 0,-3 4 0,3 8 0,0 8 0,-2-12 0,-8 20 0,10-33 0,1-15 0,1-39 0,-14-26 0,-12-17 0,0 1 0,-4-4 0,22 25 0,3 8 0,26 14 0,-5-4 0,12 6 0,-3-9 0,4-14 0,14-9 0,1-21 0,-6-3 0,-1-5 0,15-33 0,-22 28 0,-3 5 0,-5 12 0,-15 17 0,-5 30 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3667">757 1493 24575,'5'25'0,"10"16"0,0-8 0,2-1 0,5-12 0,-7-18 0,2-1 0,-3-4 0,-3-6 0,1-8 0,1-6 0,-2-13 0,-5 5 0,-14-12 0,-11 16 0,1 5 0,1 13 0,-5 9 0,14 0 0,-10 4 0,16 5 0,2-3 0,0 2 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4550">1098 1358 17431,'19'7'0,"4"47"3190,-3-8-3190,3 30 1225,-12-31-1225,0-23 646,2-15-646,-10-10 2083,18-28-2083,-7-3 0,11-19 0,-13 16 0,-3 16 0,-6 19 0,1 5 0,12 5 0,2-5 0,8-2 0,-1-9 0,23-22 0,-10-1 0,-4-10 0,-2-5 0,-1-19 0,-4-17 0,-29 9 0,0 54 0,1-9 0,5 48 0,11 22 0,1 25 0,-5-16 0,0-1 0,-10-39 0,0-8 0,1 1 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4950">1517 1309 24575,'11'-5'0,"0"2"0,21-12 0,8-14 0,3 5 0,-2-13 0,-14 17 0,-10 7 0,-3 4 0,-10 9 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7000">2466 1234 24575,'4'-3'0,"18"-1"0,-2 0 0,19 1 0,4-10 0,-4 5 0,14-16 0,-15 7 0,11-10 0,-16 12 0,-4 1 0,-13 6 0,-10 7 0,1-3 0,-9 2 0,-4 1 0,-9-3 0,-20-5 0,5-6 0,-28-27 0,22 0 0,2 2 0,16 17 0,14 21 0,-5 4 0,6-3 0,-1 4 0,8-2 0,22 6 0,24 2 0,23 3 0,-9-5 0,-1 1 0,-34-3 0,-3-1 0,-12 0 0,-10-2 0,-2 0 0,-27 44 0,-11 19 0,-5 11 0,3-6 0,-3 7 0,7-14 0,-5 9 0,1-1 0,6-7 0,-2 8 0,4-6 0,-7 8 0,7-13 0,18-29 0,12-33 0,0-1 0,0 0 0,0 4 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8817">2872 652 24575,'24'0'0,"14"-2"0,15-1 0,-2-1 0,5-2 0,2-9 0,3-2 0,10 4 0,11-4 0,5-7 0,14-8 0,3-1 0,-14 4-1160,-22 9 1,-8 2 0,7-2 1159,19-6 0,11-3 0,-4 1 0,-21 5 810,6-5-810,-34 14 0,-42 10 0,-26 6 0,2-2 0,-56-6 2668,23 2-2668,-23-5 0,28 6 0,22 1 0,11 2 0,6 0 0,11 0 0,5 2 0,21 6 0,48 10 0,17-1 0,-1-1 0,-6-10 0,-53-6 0,5 0 0,-21 11 0,-9 60 0,-25 8 0,-17 16-476,5-28 0,-9 9 1,-4 4-1,0 0 1,5-6 475,4-1 0,3-4 0,0 0 0,-4 0 0,-13 11 0,-7 3 0,3-6 0,15-15 0,5 14 0,23-64 0,0-9 0,-3-10 0,16-18 0,-8 16 0,19-13 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9517">5219 154 24575,'-4'-1'0,"-14"27"0,1 30 0,0 9 0,-9 24 0,10-8 0,8-4 0,22-24 0,4-28 0,34-67 0,-13-35 0,-10 11 0,-2-1 0,-5-17 0,-14-6 0,-40 55 0,10 18 0,-11 2 0,3 48 0,15-16 0,-11 23 0,21-31 0,3-10 0,10-15 0,-6 9 0,5-6 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink39.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-29T16:01:25.411"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.025" units="cm"/>
+      <inkml:brushProperty name="height" value="0.025" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 376 24575,'24'-3'0,"22"3"0,3 0 0,9 1 0,26 1 0,6 1 0,-25 0 0,3 1 0,1 1-316,7 0 1,2 1 0,-3 0 315,15 0 0,-6 1 116,-15-1 0,-4 0-116,-1-4 0,-6-1 0,10-1 0,5-2 0,-44-1 0,-6 0 714,19 1-714,-15 2 0,25 0 0,-30 0 0,9 0 0,-3-2 0,-7 0 0,-9-1 0,-13-3 0,-15 0 0,-27-42 0,-21-27 0,26 27 0,0 0 0,3 1 0,2 4 0,-10-6 0,14 23 0,9 20 0,7 1 0,0 5 0,6-2 0,0 0 0,1-4 0,6 5 0,5 2 0,24 4 0,14 14 0,11-1 0,21 36 0,-4-2 0,-10 1 0,-8-13 0,-21-20 0,-3 1 0,12 15 0,-11-8 0,-7-1 0,-11-14 0,-8-13 0,-4 4 0,0-3 0,-4 3 0,-3 0 0,-13 19 0,-3 4 0,-10 15 0,-6 13 0,-1 4 0,-5 2 0,4 0 0,1-3 0,6-8 0,6-9 0,8-10 0,8-6 0,6-14 0,1 1 0,1-6 0,2-10 0,2 3 0,2-5 0,4 0 0,0 3 0,4-5 0,-5 7 0,-1-5 0,0 4 0,1-15 0,-2 1 0,9-8 0,-5 2 0,6-4 0,5-8 0,1-17 0,1 11 0,0-21 0,-5 3 0,4-13 0,-4 13 0,-5 17 0,-3 21 0,-4 12 0,-1 0 0,0 4 0,-4-5 0,2 4 0,-4-2 0,3 7 0,-1 0 0,2 2 0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -9144,7 +9881,7 @@
       <c r="D50" t="s">
         <v>641</v>
       </c>
-      <c r="E50" s="119" t="s">
+      <c r="E50" s="95" t="s">
         <v>739</v>
       </c>
     </row>
@@ -9152,19 +9889,19 @@
       <c r="D51" t="s">
         <v>736</v>
       </c>
-      <c r="E51" s="119"/>
+      <c r="E51" s="95"/>
     </row>
     <row r="52" spans="3:9" x14ac:dyDescent="0.2">
       <c r="D52" t="s">
         <v>737</v>
       </c>
-      <c r="E52" s="119"/>
+      <c r="E52" s="95"/>
     </row>
     <row r="53" spans="3:9" x14ac:dyDescent="0.2">
       <c r="D53" t="s">
         <v>738</v>
       </c>
-      <c r="E53" s="119"/>
+      <c r="E53" s="95"/>
     </row>
     <row r="56" spans="3:9" x14ac:dyDescent="0.2">
       <c r="C56" t="s">
@@ -9349,25 +10086,25 @@
       </c>
     </row>
     <row r="69" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C69" s="120">
+      <c r="C69" s="94">
         <v>1</v>
       </c>
-      <c r="D69" s="120" t="s">
+      <c r="D69" s="94" t="s">
         <v>611</v>
       </c>
-      <c r="E69" s="120">
+      <c r="E69" s="94">
         <v>1</v>
       </c>
-      <c r="F69" s="120">
+      <c r="F69" s="94">
         <v>2</v>
       </c>
-      <c r="G69" s="120" t="s">
+      <c r="G69" s="94" t="s">
         <v>645</v>
       </c>
-      <c r="H69" s="120">
+      <c r="H69" s="94">
         <v>1</v>
       </c>
-      <c r="J69" s="120" t="s">
+      <c r="J69" s="94" t="s">
         <v>744</v>
       </c>
       <c r="K69">
@@ -9375,25 +10112,25 @@
       </c>
     </row>
     <row r="70" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C70" s="120">
+      <c r="C70" s="94">
         <v>1</v>
       </c>
-      <c r="D70" s="120" t="s">
+      <c r="D70" s="94" t="s">
         <v>611</v>
       </c>
-      <c r="E70" s="120">
+      <c r="E70" s="94">
         <v>1</v>
       </c>
-      <c r="F70" s="120">
+      <c r="F70" s="94">
         <v>3</v>
       </c>
-      <c r="G70" s="120" t="s">
+      <c r="G70" s="94" t="s">
         <v>646</v>
       </c>
-      <c r="H70" s="120">
+      <c r="H70" s="94">
         <v>1</v>
       </c>
-      <c r="J70" s="120" t="s">
+      <c r="J70" s="94" t="s">
         <v>745</v>
       </c>
       <c r="K70">
@@ -9453,25 +10190,25 @@
       </c>
     </row>
     <row r="73" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C73" s="120">
+      <c r="C73" s="94">
         <v>2</v>
       </c>
-      <c r="D73" s="120" t="s">
+      <c r="D73" s="94" t="s">
         <v>645</v>
       </c>
-      <c r="E73" s="120">
+      <c r="E73" s="94">
         <v>1</v>
       </c>
-      <c r="F73" s="120">
+      <c r="F73" s="94">
         <v>3</v>
       </c>
-      <c r="G73" s="120" t="s">
+      <c r="G73" s="94" t="s">
         <v>646</v>
       </c>
-      <c r="H73" s="120">
+      <c r="H73" s="94">
         <v>1</v>
       </c>
-      <c r="J73" s="120" t="s">
+      <c r="J73" s="94" t="s">
         <v>748</v>
       </c>
       <c r="K73">
@@ -9583,25 +10320,25 @@
       </c>
     </row>
     <row r="78" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C78" s="120">
+      <c r="C78" s="94">
         <v>4</v>
       </c>
-      <c r="D78" s="120" t="s">
+      <c r="D78" s="94" t="s">
         <v>647</v>
       </c>
-      <c r="E78" s="120">
+      <c r="E78" s="94">
         <v>2</v>
       </c>
-      <c r="F78" s="120">
+      <c r="F78" s="94">
         <v>5</v>
       </c>
-      <c r="G78" s="120" t="s">
+      <c r="G78" s="94" t="s">
         <v>648</v>
       </c>
-      <c r="H78" s="120">
+      <c r="H78" s="94">
         <v>2</v>
       </c>
-      <c r="J78" s="120" t="s">
+      <c r="J78" s="94" t="s">
         <v>753</v>
       </c>
       <c r="K78">
@@ -10429,14 +11166,14 @@
       </c>
     </row>
     <row r="166" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C166" s="119" t="s">
+      <c r="C166" s="95" t="s">
         <v>726</v>
       </c>
-      <c r="D166" s="119"/>
-      <c r="G166" s="119" t="s">
+      <c r="D166" s="95"/>
+      <c r="G166" s="95" t="s">
         <v>588</v>
       </c>
-      <c r="H166" s="119"/>
+      <c r="H166" s="95"/>
     </row>
     <row r="167" spans="3:8" x14ac:dyDescent="0.2">
       <c r="C167" s="1">
@@ -10586,6 +11323,418 @@
     <mergeCell ref="E50:E53"/>
     <mergeCell ref="C166:D166"/>
     <mergeCell ref="G166:H166"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C17B837-974D-B54B-ABEA-DED5637FC833}">
+  <dimension ref="B6:M87"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="20.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="6" spans="12:13" x14ac:dyDescent="0.2">
+      <c r="L6" t="s">
+        <v>94</v>
+      </c>
+      <c r="M6" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="7" spans="12:13" x14ac:dyDescent="0.2">
+      <c r="L7" t="s">
+        <v>308</v>
+      </c>
+      <c r="M7" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="13" spans="12:13" x14ac:dyDescent="0.2">
+      <c r="L13" t="s">
+        <v>561</v>
+      </c>
+      <c r="M13" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="14" spans="12:13" x14ac:dyDescent="0.2">
+      <c r="L14" t="s">
+        <v>562</v>
+      </c>
+      <c r="M14" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="26" spans="11:11" x14ac:dyDescent="0.2">
+      <c r="K26" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="27" spans="11:11" x14ac:dyDescent="0.2">
+      <c r="K27" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="28" spans="11:11" x14ac:dyDescent="0.2">
+      <c r="K28" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="29" spans="11:11" x14ac:dyDescent="0.2">
+      <c r="K29" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="30" spans="11:11" x14ac:dyDescent="0.2">
+      <c r="K30" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C37" t="s">
+        <v>284</v>
+      </c>
+      <c r="E37" t="s">
+        <v>780</v>
+      </c>
+      <c r="G37" s="111" t="s">
+        <v>781</v>
+      </c>
+      <c r="H37" s="111"/>
+      <c r="I37" s="111"/>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="E39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="E40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="E41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="E42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="E43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="E44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="E45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="E46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+    </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="E47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+    </row>
+    <row r="48" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="E48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+    </row>
+    <row r="49" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="E49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+    </row>
+    <row r="50" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+    </row>
+    <row r="51" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C52" s="121" t="s">
+        <v>782</v>
+      </c>
+      <c r="E52" s="121" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="53" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C53" s="122"/>
+      <c r="E53" s="122"/>
+    </row>
+    <row r="54" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C54" s="122"/>
+      <c r="E54" s="122"/>
+    </row>
+    <row r="55" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C55" s="123"/>
+      <c r="E55" s="123"/>
+    </row>
+    <row r="63" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
+    </row>
+    <row r="64" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="J64" s="1"/>
+      <c r="K64" s="1"/>
+      <c r="L64" s="1"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="1"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="J70" s="1"/>
+      <c r="K70" s="1"/>
+      <c r="L70" s="1"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="J71" s="1"/>
+      <c r="K71" s="1"/>
+      <c r="L71" s="1"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B72" s="1"/>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="J72" s="1"/>
+      <c r="K72" s="1"/>
+      <c r="L72" s="1"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="J73" s="1"/>
+      <c r="K73" s="1"/>
+      <c r="L73" s="1"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B74" s="1"/>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="J74" s="1"/>
+      <c r="K74" s="1"/>
+      <c r="L74" s="1"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B77" s="1"/>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+    </row>
+    <row r="84" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B84" t="s">
+        <v>284</v>
+      </c>
+      <c r="D84" t="s">
+        <v>780</v>
+      </c>
+      <c r="F84" s="111" t="s">
+        <v>781</v>
+      </c>
+      <c r="G84" s="111"/>
+      <c r="H84" s="111"/>
+    </row>
+    <row r="85" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B85" t="s">
+        <v>274</v>
+      </c>
+      <c r="D85" t="s">
+        <v>548</v>
+      </c>
+      <c r="E85" s="95" t="s">
+        <v>784</v>
+      </c>
+      <c r="G85" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B86" t="s">
+        <v>548</v>
+      </c>
+      <c r="D86" t="s">
+        <v>582</v>
+      </c>
+      <c r="E86" s="95"/>
+      <c r="G86" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="87" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B87" t="s">
+        <v>582</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="C52:C55"/>
+    <mergeCell ref="E52:E55"/>
+    <mergeCell ref="F84:H84"/>
+    <mergeCell ref="E85:E86"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -13172,7 +14321,7 @@
       </c>
       <c r="J56" t="str">
         <f ca="1">TEXT(NOW(),"YYYY-MM-DD")</f>
-        <v>2026-08-23</v>
+        <v>2026-08-29</v>
       </c>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.2">
@@ -13181,7 +14330,7 @@
       </c>
       <c r="J57" t="str">
         <f ca="1">TEXT(NOW(),"dddd, mmm DD yyyy")</f>
-        <v>Sunday, Aug 23 2026</v>
+        <v>Saturday, Aug 29 2026</v>
       </c>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.2">
@@ -15897,17 +17046,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="111" t="s">
         <v>585</v>
       </c>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="109"/>
-      <c r="G2" s="109" t="s">
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="G2" s="111" t="s">
         <v>586</v>
       </c>
-      <c r="H2" s="109"/>
-      <c r="I2" s="109"/>
+      <c r="H2" s="111"/>
+      <c r="I2" s="111"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="41"/>
@@ -16041,12 +17190,12 @@
       <c r="F20" s="52"/>
       <c r="G20" s="53"/>
       <c r="H20" s="54"/>
-      <c r="J20" s="110" t="s">
+      <c r="J20" s="112" t="s">
         <v>587</v>
       </c>
-      <c r="K20" s="111"/>
-      <c r="L20" s="111"/>
-      <c r="M20" s="112"/>
+      <c r="K20" s="113"/>
+      <c r="L20" s="113"/>
+      <c r="M20" s="114"/>
       <c r="O20" t="s">
         <v>590</v>
       </c>
@@ -16059,10 +17208,10 @@
       <c r="F21" s="52"/>
       <c r="G21" s="53"/>
       <c r="H21" s="54"/>
-      <c r="J21" s="113"/>
-      <c r="K21" s="114"/>
-      <c r="L21" s="114"/>
-      <c r="M21" s="115"/>
+      <c r="J21" s="115"/>
+      <c r="K21" s="116"/>
+      <c r="L21" s="116"/>
+      <c r="M21" s="117"/>
       <c r="P21" t="s">
         <v>592</v>
       </c>
@@ -16075,10 +17224,10 @@
       <c r="F22" s="52"/>
       <c r="G22" s="53"/>
       <c r="H22" s="54"/>
-      <c r="J22" s="113"/>
-      <c r="K22" s="114"/>
-      <c r="L22" s="114"/>
-      <c r="M22" s="115"/>
+      <c r="J22" s="115"/>
+      <c r="K22" s="116"/>
+      <c r="L22" s="116"/>
+      <c r="M22" s="117"/>
       <c r="Q22" t="s">
         <v>594</v>
       </c>
@@ -16091,10 +17240,10 @@
       <c r="F23" s="52"/>
       <c r="G23" s="53"/>
       <c r="H23" s="54"/>
-      <c r="J23" s="116"/>
-      <c r="K23" s="117"/>
-      <c r="L23" s="117"/>
-      <c r="M23" s="118"/>
+      <c r="J23" s="118"/>
+      <c r="K23" s="119"/>
+      <c r="L23" s="119"/>
+      <c r="M23" s="120"/>
       <c r="P23" t="s">
         <v>593</v>
       </c>
@@ -16107,12 +17256,12 @@
       <c r="F24" s="52"/>
       <c r="G24" s="53"/>
       <c r="H24" s="54"/>
-      <c r="J24" s="94" t="s">
+      <c r="J24" s="96" t="s">
         <v>589</v>
       </c>
-      <c r="K24" s="95"/>
-      <c r="L24" s="95"/>
-      <c r="M24" s="96"/>
+      <c r="K24" s="97"/>
+      <c r="L24" s="97"/>
+      <c r="M24" s="98"/>
       <c r="O24" t="s">
         <v>591</v>
       </c>
@@ -16125,28 +17274,28 @@
       <c r="F25" s="52"/>
       <c r="G25" s="53"/>
       <c r="H25" s="54"/>
-      <c r="J25" s="97"/>
-      <c r="K25" s="98"/>
-      <c r="L25" s="98"/>
-      <c r="M25" s="99"/>
+      <c r="J25" s="99"/>
+      <c r="K25" s="100"/>
+      <c r="L25" s="100"/>
+      <c r="M25" s="101"/>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.2">
       <c r="F26" s="52"/>
       <c r="G26" s="53"/>
       <c r="H26" s="54"/>
-      <c r="J26" s="97"/>
-      <c r="K26" s="98"/>
-      <c r="L26" s="98"/>
-      <c r="M26" s="99"/>
+      <c r="J26" s="99"/>
+      <c r="K26" s="100"/>
+      <c r="L26" s="100"/>
+      <c r="M26" s="101"/>
     </row>
     <row r="27" spans="2:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="F27" s="52"/>
       <c r="G27" s="53"/>
       <c r="H27" s="54"/>
-      <c r="J27" s="100"/>
-      <c r="K27" s="101"/>
-      <c r="L27" s="101"/>
-      <c r="M27" s="102"/>
+      <c r="J27" s="102"/>
+      <c r="K27" s="103"/>
+      <c r="L27" s="103"/>
+      <c r="M27" s="104"/>
       <c r="O27" t="s">
         <v>595</v>
       </c>
@@ -16188,22 +17337,22 @@
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="45"/>
-      <c r="J35" s="110" t="s">
+      <c r="J35" s="112" t="s">
         <v>588</v>
       </c>
-      <c r="K35" s="111"/>
-      <c r="L35" s="111"/>
-      <c r="M35" s="112"/>
+      <c r="K35" s="113"/>
+      <c r="L35" s="113"/>
+      <c r="M35" s="114"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B36" s="44"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="45"/>
-      <c r="J36" s="113"/>
-      <c r="K36" s="114"/>
-      <c r="L36" s="114"/>
-      <c r="M36" s="115"/>
+      <c r="J36" s="115"/>
+      <c r="K36" s="116"/>
+      <c r="L36" s="116"/>
+      <c r="M36" s="117"/>
       <c r="O36" t="s">
         <v>598</v>
       </c>
@@ -16216,10 +17365,10 @@
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="45"/>
-      <c r="J37" s="113"/>
-      <c r="K37" s="114"/>
-      <c r="L37" s="114"/>
-      <c r="M37" s="115"/>
+      <c r="J37" s="115"/>
+      <c r="K37" s="116"/>
+      <c r="L37" s="116"/>
+      <c r="M37" s="117"/>
       <c r="O37" t="s">
         <v>599</v>
       </c>
@@ -16232,22 +17381,22 @@
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="45"/>
-      <c r="J38" s="116"/>
-      <c r="K38" s="117"/>
-      <c r="L38" s="117"/>
-      <c r="M38" s="118"/>
+      <c r="J38" s="118"/>
+      <c r="K38" s="119"/>
+      <c r="L38" s="119"/>
+      <c r="M38" s="120"/>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B39" s="44"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="45"/>
-      <c r="J39" s="94" t="s">
+      <c r="J39" s="96" t="s">
         <v>600</v>
       </c>
-      <c r="K39" s="95"/>
-      <c r="L39" s="95"/>
-      <c r="M39" s="96"/>
+      <c r="K39" s="97"/>
+      <c r="L39" s="97"/>
+      <c r="M39" s="98"/>
       <c r="O39" t="s">
         <v>598</v>
       </c>
@@ -16266,10 +17415,10 @@
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="45"/>
-      <c r="J40" s="97"/>
-      <c r="K40" s="98"/>
-      <c r="L40" s="98"/>
-      <c r="M40" s="99"/>
+      <c r="J40" s="99"/>
+      <c r="K40" s="100"/>
+      <c r="L40" s="100"/>
+      <c r="M40" s="101"/>
       <c r="O40" t="s">
         <v>599</v>
       </c>
@@ -16288,10 +17437,10 @@
       <c r="C41" s="47"/>
       <c r="D41" s="47"/>
       <c r="E41" s="48"/>
-      <c r="J41" s="97"/>
-      <c r="K41" s="98"/>
-      <c r="L41" s="98"/>
-      <c r="M41" s="99"/>
+      <c r="J41" s="99"/>
+      <c r="K41" s="100"/>
+      <c r="L41" s="100"/>
+      <c r="M41" s="101"/>
     </row>
     <row r="42" spans="2:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B42" s="49" t="s">
@@ -16306,52 +17455,52 @@
       <c r="E42" s="59" t="s">
         <v>602</v>
       </c>
-      <c r="J42" s="100"/>
-      <c r="K42" s="101"/>
-      <c r="L42" s="101"/>
-      <c r="M42" s="102"/>
+      <c r="J42" s="102"/>
+      <c r="K42" s="103"/>
+      <c r="L42" s="103"/>
+      <c r="M42" s="104"/>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B43" s="52"/>
       <c r="C43" s="53"/>
       <c r="D43" s="54"/>
       <c r="E43" s="60"/>
-      <c r="J43" s="94" t="s">
+      <c r="J43" s="96" t="s">
         <v>601</v>
       </c>
-      <c r="K43" s="95"/>
-      <c r="L43" s="95"/>
-      <c r="M43" s="96"/>
+      <c r="K43" s="97"/>
+      <c r="L43" s="97"/>
+      <c r="M43" s="98"/>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B44" s="52"/>
       <c r="C44" s="53"/>
       <c r="D44" s="54"/>
       <c r="E44" s="60"/>
-      <c r="J44" s="97"/>
-      <c r="K44" s="98"/>
-      <c r="L44" s="98"/>
-      <c r="M44" s="99"/>
+      <c r="J44" s="99"/>
+      <c r="K44" s="100"/>
+      <c r="L44" s="100"/>
+      <c r="M44" s="101"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B45" s="52"/>
       <c r="C45" s="53"/>
       <c r="D45" s="54"/>
       <c r="E45" s="60"/>
-      <c r="J45" s="97"/>
-      <c r="K45" s="98"/>
-      <c r="L45" s="98"/>
-      <c r="M45" s="99"/>
+      <c r="J45" s="99"/>
+      <c r="K45" s="100"/>
+      <c r="L45" s="100"/>
+      <c r="M45" s="101"/>
     </row>
     <row r="46" spans="2:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B46" s="52"/>
       <c r="C46" s="53"/>
       <c r="D46" s="54"/>
       <c r="E46" s="60"/>
-      <c r="J46" s="100"/>
-      <c r="K46" s="101"/>
-      <c r="L46" s="101"/>
-      <c r="M46" s="102"/>
+      <c r="J46" s="102"/>
+      <c r="K46" s="103"/>
+      <c r="L46" s="103"/>
+      <c r="M46" s="104"/>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B47" s="52"/>
@@ -16402,12 +17551,12 @@
     </row>
     <row r="58" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="59" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="E59" s="103" t="s">
+      <c r="E59" s="105" t="s">
         <v>608</v>
       </c>
-      <c r="F59" s="104"/>
-      <c r="G59" s="104"/>
-      <c r="H59" s="105"/>
+      <c r="F59" s="106"/>
+      <c r="G59" s="106"/>
+      <c r="H59" s="107"/>
       <c r="J59" t="s">
         <v>609</v>
       </c>
@@ -16416,10 +17565,10 @@
       <c r="B60" t="s">
         <v>604</v>
       </c>
-      <c r="E60" s="106"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="110"/>
     </row>
     <row r="61" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
